--- a/backend_py/stackwealth/excel_engine/master/cfp_master.xlsx
+++ b/backend_py/stackwealth/excel_engine/master/cfp_master.xlsx
@@ -47576,7 +47576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A2:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="12.25" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -47602,7 +47602,6 @@
     <col width="10.33203125" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="126" t="inlineStr">
         <is>
@@ -47650,38 +47649,158 @@
       <c r="S3" s="155" t="n"/>
     </row>
     <row r="4" ht="55" customFormat="1" customHeight="1" s="127">
-      <c r="B4" s="156" t="n"/>
-      <c r="C4" s="156" t="n"/>
-      <c r="D4" s="156" t="n"/>
-      <c r="E4" s="156" t="n"/>
-      <c r="F4" s="156" t="n"/>
-      <c r="G4" s="156" t="n"/>
-      <c r="H4" s="156" t="n"/>
-      <c r="I4" s="156" t="n"/>
-      <c r="J4" s="156" t="n"/>
-      <c r="K4" s="156" t="n"/>
-      <c r="L4" s="156" t="n"/>
-      <c r="M4" s="156" t="n"/>
-      <c r="N4" s="376" t="n"/>
-      <c r="O4" s="156" t="n"/>
-      <c r="P4" s="156" t="n"/>
-      <c r="Q4" s="156" t="n"/>
-      <c r="R4" s="156" t="n"/>
-      <c r="S4" s="156" t="n"/>
-      <c r="T4" s="381" t="n"/>
-      <c r="U4" s="156" t="n"/>
-      <c r="V4" s="156" t="n"/>
-      <c r="W4" s="376" t="n"/>
-      <c r="X4" s="156" t="n"/>
-      <c r="Y4" s="156" t="n"/>
-      <c r="Z4" s="156" t="n"/>
-      <c r="AA4" s="156" t="n"/>
-      <c r="AB4" s="376" t="n"/>
-      <c r="AC4" s="360" t="n"/>
-      <c r="AD4" s="360" t="n"/>
+      <c r="B4" s="156" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C4" s="156" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D4" s="156" t="inlineStr">
+        <is>
+          <t>Age  of Primary Client</t>
+        </is>
+      </c>
+      <c r="E4" s="156" t="inlineStr">
+        <is>
+          <t>Income form Employment</t>
+        </is>
+      </c>
+      <c r="F4" s="156" t="inlineStr">
+        <is>
+          <t>Income from  business/profession</t>
+        </is>
+      </c>
+      <c r="G4" s="156" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
+      <c r="H4" s="156" t="inlineStr">
+        <is>
+          <t>Income from Others sources / non financial assets</t>
+        </is>
+      </c>
+      <c r="I4" s="156" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="J4" s="156" t="inlineStr">
+        <is>
+          <t>Regular Expenses (Except Loans and Major One Time)</t>
+        </is>
+      </c>
+      <c r="K4" s="156" t="inlineStr">
+        <is>
+          <t>Loan Repayments</t>
+        </is>
+      </c>
+      <c r="L4" s="156" t="inlineStr">
+        <is>
+          <t>Total Outflow</t>
+        </is>
+      </c>
+      <c r="M4" s="156" t="inlineStr">
+        <is>
+          <t>Surplus</t>
+        </is>
+      </c>
+      <c r="N4" s="376" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O4" s="156" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="P4" s="156" t="inlineStr">
+        <is>
+          <t>Opening Balance of Finanical Assets</t>
+        </is>
+      </c>
+      <c r="Q4" s="156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Net Annual Cash Savings (Family) </t>
+        </is>
+      </c>
+      <c r="R4" s="156" t="inlineStr">
+        <is>
+          <t>Major Withdrawls</t>
+        </is>
+      </c>
+      <c r="S4" s="156" t="inlineStr">
+        <is>
+          <t>Income from investments</t>
+        </is>
+      </c>
+      <c r="T4" s="381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumpsum Further deposit / (Withdrawl) </t>
+        </is>
+      </c>
+      <c r="U4" s="156" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="V4" s="156" t="inlineStr">
+        <is>
+          <t>Closing Balance of Financial Assets</t>
+        </is>
+      </c>
+      <c r="W4" s="376" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X4" s="156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opening Balance of Non Finanical Assets (Mostly Real Estate / Gold) </t>
+        </is>
+      </c>
+      <c r="Y4" s="156" t="inlineStr">
+        <is>
+          <t>Addition / (Disposal) of Fixed Assets</t>
+        </is>
+      </c>
+      <c r="Z4" s="156" t="inlineStr">
+        <is>
+          <t>Appreciation/(Depreciation)</t>
+        </is>
+      </c>
+      <c r="AA4" s="156" t="inlineStr">
+        <is>
+          <t>Closing Balance of Non Finanical Assets</t>
+        </is>
+      </c>
+      <c r="AB4" s="376" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AC4" s="360" t="inlineStr">
+        <is>
+          <t>Total Networth</t>
+        </is>
+      </c>
+      <c r="AD4" s="360" t="inlineStr">
+        <is>
+          <t>Total Networth INR Crore</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="365" t="n"/>
+      <c r="B5" s="365" t="inlineStr">
+        <is>
+          <t>Increase YoY (Net of Taxes) %</t>
+        </is>
+      </c>
       <c r="C5" s="365" t="n"/>
       <c r="D5" s="365" t="n"/>
       <c r="E5" s="482">
@@ -47705,11 +47824,19 @@
         <f>'Assumptions &amp; Computation'!D3</f>
         <v/>
       </c>
-      <c r="K5" s="482" t="n"/>
+      <c r="K5" s="482" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
       <c r="L5" s="367" t="n"/>
       <c r="M5" s="365" t="n"/>
       <c r="O5" s="365" t="n"/>
-      <c r="P5" s="367" t="n"/>
+      <c r="P5" s="367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Real Estate (Not considered  for earnings or increase in valuation) </t>
+        </is>
+      </c>
       <c r="Q5" s="365" t="n"/>
       <c r="R5" s="482" t="n"/>
       <c r="S5" s="483">
@@ -47731,8 +47858,14 @@
       <c r="AD5" s="51" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="32" t="n"/>
-      <c r="C6" s="51" t="n"/>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Y0</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="n">
+        <v>2026</v>
+      </c>
       <c r="D6" s="257">
         <f>'1_Personal_Details'!D5</f>
         <v/>
@@ -47824,7 +47957,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="32" t="n"/>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
       <c r="C7" s="51">
         <f>C6+1</f>
         <v/>
@@ -47917,7 +48054,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="32" t="n"/>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
       <c r="C8" s="51">
         <f>C7+1</f>
         <v/>
@@ -48010,7 +48151,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="32" t="n"/>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
       <c r="C9" s="51">
         <f>C8+1</f>
         <v/>
@@ -48072,8 +48217,14 @@
         <f>(P9+Q9/2-R9)*(S$5)</f>
         <v/>
       </c>
-      <c r="T9" s="158" t="n"/>
-      <c r="U9" s="453" t="n"/>
+      <c r="T9" s="158" t="n">
+        <v>200000</v>
+      </c>
+      <c r="U9" s="453" t="inlineStr">
+        <is>
+          <t>Bonus Expected</t>
+        </is>
+      </c>
       <c r="V9" s="377">
         <f>P9+Q9+R9+S9+T9</f>
         <v/>
@@ -48103,7 +48254,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="32" t="n"/>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
       <c r="C10" s="51">
         <f>C9+1</f>
         <v/>
@@ -48196,7 +48351,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="32" t="n"/>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
       <c r="C11" s="51">
         <f>C10+1</f>
         <v/>
@@ -48289,7 +48448,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="32" t="n"/>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
       <c r="C12" s="51">
         <f>C11+1</f>
         <v/>
@@ -48382,7 +48545,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="32" t="n"/>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
       <c r="C13" s="51">
         <f>C12+1</f>
         <v/>
@@ -48475,7 +48642,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="32" t="n"/>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
       <c r="C14" s="51">
         <f>C13+1</f>
         <v/>
@@ -48568,7 +48739,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="32" t="n"/>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
       <c r="C15" s="51">
         <f>C14+1</f>
         <v/>
@@ -48661,7 +48836,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="32" t="n"/>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
       <c r="C16" s="51">
         <f>C15+1</f>
         <v/>
@@ -48751,7 +48930,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="n"/>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Y11</t>
+        </is>
+      </c>
       <c r="C17" s="51">
         <f>C16+1</f>
         <v/>
@@ -48810,8 +48993,14 @@
         <f>(P17+Q17/2-R17)*(S$5)</f>
         <v/>
       </c>
-      <c r="T17" s="158" t="n"/>
-      <c r="U17" s="453" t="n"/>
+      <c r="T17" s="158" t="n">
+        <v>-500000</v>
+      </c>
+      <c r="U17" s="453" t="inlineStr">
+        <is>
+          <t>Knee Surgery planned for parents who don’t have insurance</t>
+        </is>
+      </c>
       <c r="V17" s="377">
         <f>P17+Q17+R17+S17+T17</f>
         <v/>
@@ -48841,7 +49030,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="32" t="n"/>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Y12</t>
+        </is>
+      </c>
       <c r="C18" s="51">
         <f>C17+1</f>
         <v/>
@@ -48931,7 +49124,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="32" t="n"/>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Y13</t>
+        </is>
+      </c>
       <c r="C19" s="51">
         <f>C18+1</f>
         <v/>
@@ -49021,7 +49218,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="32" t="n"/>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Y14</t>
+        </is>
+      </c>
       <c r="C20" s="51">
         <f>C19+1</f>
         <v/>
@@ -49111,7 +49312,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="32" t="n"/>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Y15</t>
+        </is>
+      </c>
       <c r="C21" s="51">
         <f>C20+1</f>
         <v/>
@@ -49201,7 +49406,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="32" t="n"/>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Y16</t>
+        </is>
+      </c>
       <c r="C22" s="51">
         <f>C21+1</f>
         <v/>
@@ -49291,7 +49500,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="32" t="n"/>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>Y17</t>
+        </is>
+      </c>
       <c r="C23" s="51">
         <f>C22+1</f>
         <v/>
@@ -49382,7 +49595,11 @@
     </row>
     <row r="24">
       <c r="A24" s="486" t="n"/>
-      <c r="B24" s="32" t="n"/>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Y18</t>
+        </is>
+      </c>
       <c r="C24" s="51">
         <f>C23+1</f>
         <v/>
@@ -49472,7 +49689,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="32" t="n"/>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>Y19</t>
+        </is>
+      </c>
       <c r="C25" s="51">
         <f>C24+1</f>
         <v/>
@@ -49570,7 +49791,11 @@
           <t>Retirement Age</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n"/>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Y20</t>
+        </is>
+      </c>
       <c r="C26" s="51">
         <f>C25+1</f>
         <v/>
@@ -49663,7 +49888,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="32" t="n"/>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>Y21</t>
+        </is>
+      </c>
       <c r="C27" s="51">
         <f>C26+1</f>
         <v/>
@@ -49753,7 +49982,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="32" t="n"/>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>Y22</t>
+        </is>
+      </c>
       <c r="C28" s="51">
         <f>C27+1</f>
         <v/>
@@ -49843,7 +50076,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="32" t="n"/>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>Y23</t>
+        </is>
+      </c>
       <c r="C29" s="51">
         <f>C28+1</f>
         <v/>
@@ -49938,7 +50175,11 @@
           <t>Business Income Ceases</t>
         </is>
       </c>
-      <c r="B30" s="32" t="n"/>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>Y24</t>
+        </is>
+      </c>
       <c r="C30" s="51">
         <f>C29+1</f>
         <v/>
@@ -49997,8 +50238,14 @@
         <f>(P30+Q30/2-R30)*(S$5)</f>
         <v/>
       </c>
-      <c r="T30" s="378" t="n"/>
-      <c r="U30" s="158" t="n"/>
+      <c r="T30" s="378" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U30" s="158" t="inlineStr">
+        <is>
+          <t>Reverse Mortgage</t>
+        </is>
+      </c>
       <c r="V30" s="377">
         <f>P30+Q30+R30+S30+T30</f>
         <v/>
@@ -50028,7 +50275,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="32" t="n"/>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>Y25</t>
+        </is>
+      </c>
       <c r="C31" s="51">
         <f>C30+1</f>
         <v/>
@@ -50115,7 +50366,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="32" t="n"/>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Y26</t>
+        </is>
+      </c>
       <c r="C32" s="51">
         <f>C31+1</f>
         <v/>
@@ -50171,8 +50426,14 @@
         <f>(P32+Q32/2-R32)*(S$5)</f>
         <v/>
       </c>
-      <c r="T32" s="378" t="n"/>
-      <c r="U32" s="158" t="n"/>
+      <c r="T32" s="378" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U32" s="158" t="inlineStr">
+        <is>
+          <t>Reverse Mortgage</t>
+        </is>
+      </c>
       <c r="V32" s="377">
         <f>P32+Q32+R32+S32+T32</f>
         <v/>
@@ -50202,7 +50463,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="32" t="n"/>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>Y27</t>
+        </is>
+      </c>
       <c r="C33" s="51">
         <f>C32+1</f>
         <v/>
@@ -50289,7 +50554,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="32" t="n"/>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>Y28</t>
+        </is>
+      </c>
       <c r="C34" s="51">
         <f>C33+1</f>
         <v/>
@@ -50345,8 +50614,14 @@
         <f>(P34+Q34/2-R34)*(S$5)</f>
         <v/>
       </c>
-      <c r="T34" s="378" t="n"/>
-      <c r="U34" s="158" t="n"/>
+      <c r="T34" s="378" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U34" s="158" t="inlineStr">
+        <is>
+          <t>Reverse Mortgage</t>
+        </is>
+      </c>
       <c r="V34" s="377">
         <f>P34+Q34+R34+S34+T34</f>
         <v/>
@@ -50376,7 +50651,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="32" t="n"/>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>Y29</t>
+        </is>
+      </c>
       <c r="C35" s="51">
         <f>C34+1</f>
         <v/>
@@ -50463,7 +50742,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="32" t="n"/>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>Y30</t>
+        </is>
+      </c>
       <c r="C36" s="51">
         <f>C35+1</f>
         <v/>
@@ -50519,8 +50802,14 @@
         <f>(P36+Q36/2-R36)*(S$5)</f>
         <v/>
       </c>
-      <c r="T36" s="378" t="n"/>
-      <c r="U36" s="158" t="n"/>
+      <c r="T36" s="378" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U36" s="158" t="inlineStr">
+        <is>
+          <t>Reverse Mortgage</t>
+        </is>
+      </c>
       <c r="V36" s="377">
         <f>P36+Q36+R36+S36+T36</f>
         <v/>
@@ -50550,7 +50839,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="32" t="n"/>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>Y31</t>
+        </is>
+      </c>
       <c r="C37" s="51">
         <f>C36+1</f>
         <v/>
@@ -50637,7 +50930,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="32" t="n"/>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>Y32</t>
+        </is>
+      </c>
       <c r="C38" s="51">
         <f>C37+1</f>
         <v/>
@@ -50693,8 +50990,14 @@
         <f>(P38+Q38/2-R38)*(S$5)</f>
         <v/>
       </c>
-      <c r="T38" s="378" t="n"/>
-      <c r="U38" s="158" t="n"/>
+      <c r="T38" s="378" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U38" s="158" t="inlineStr">
+        <is>
+          <t>Reverse Mortgage</t>
+        </is>
+      </c>
       <c r="V38" s="377">
         <f>P38+Q38+R38+S38+T38</f>
         <v/>
@@ -50724,7 +51027,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="32" t="n"/>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>Y33</t>
+        </is>
+      </c>
       <c r="C39" s="51">
         <f>C38+1</f>
         <v/>
@@ -50811,7 +51118,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="32" t="n"/>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>Y34</t>
+        </is>
+      </c>
       <c r="C40" s="51">
         <f>C39+1</f>
         <v/>
@@ -50898,7 +51209,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="32" t="n"/>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>Y35</t>
+        </is>
+      </c>
       <c r="C41" s="51">
         <f>C40+1</f>
         <v/>
@@ -50985,7 +51300,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="32" t="n"/>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>Y36</t>
+        </is>
+      </c>
       <c r="C42" s="51">
         <f>C41+1</f>
         <v/>
@@ -51072,7 +51391,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="32" t="n"/>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Y37</t>
+        </is>
+      </c>
       <c r="C43" s="51">
         <f>C42+1</f>
         <v/>
@@ -51159,7 +51482,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="32" t="n"/>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>Y38</t>
+        </is>
+      </c>
       <c r="C44" s="51">
         <f>C43+1</f>
         <v/>
@@ -51246,7 +51573,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="32" t="n"/>
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>Y39</t>
+        </is>
+      </c>
       <c r="C45" s="51">
         <f>C44+1</f>
         <v/>
@@ -51333,7 +51664,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="32" t="n"/>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>Y40</t>
+        </is>
+      </c>
       <c r="C46" s="51">
         <f>C45+1</f>
         <v/>
@@ -51420,7 +51755,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="32" t="n"/>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>Y41</t>
+        </is>
+      </c>
       <c r="C47" s="51">
         <f>C46+1</f>
         <v/>
@@ -51507,7 +51846,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="32" t="n"/>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>Y42</t>
+        </is>
+      </c>
       <c r="C48" s="51">
         <f>C47+1</f>
         <v/>
@@ -51594,7 +51937,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="32" t="n"/>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>Y43</t>
+        </is>
+      </c>
       <c r="C49" s="51">
         <f>C48+1</f>
         <v/>
@@ -51681,7 +52028,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="32" t="n"/>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>Y44</t>
+        </is>
+      </c>
       <c r="C50" s="51">
         <f>C49+1</f>
         <v/>
@@ -51768,7 +52119,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="32" t="n"/>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>Y45</t>
+        </is>
+      </c>
       <c r="C51" s="51">
         <f>C50+1</f>
         <v/>
@@ -51855,7 +52210,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="32" t="n"/>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>Y46</t>
+        </is>
+      </c>
       <c r="C52" s="51">
         <f>C51+1</f>
         <v/>
@@ -51942,7 +52301,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="32" t="n"/>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>Y47</t>
+        </is>
+      </c>
       <c r="C53" s="51">
         <f>C52+1</f>
         <v/>
@@ -52029,7 +52392,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="32" t="n"/>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>Y48</t>
+        </is>
+      </c>
       <c r="C54" s="51">
         <f>C53+1</f>
         <v/>
@@ -52116,7 +52483,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="32" t="n"/>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>Y49</t>
+        </is>
+      </c>
       <c r="C55" s="51">
         <f>C54+1</f>
         <v/>
@@ -52203,7 +52574,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="32" t="n"/>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>Y50</t>
+        </is>
+      </c>
       <c r="C56" s="51">
         <f>C55+1</f>
         <v/>
@@ -52259,8 +52634,14 @@
         <f>(P56+Q56/2-R56)*(S$5)</f>
         <v/>
       </c>
-      <c r="T56" s="158" t="n"/>
-      <c r="U56" s="453" t="n"/>
+      <c r="T56" s="158" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="U56" s="453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance sale consideration after closure of reverse mortgage </t>
+        </is>
+      </c>
       <c r="V56" s="377">
         <f>P56+Q56+R56+S56+T56</f>
         <v/>
@@ -52270,7 +52651,9 @@
         <f>AA55</f>
         <v/>
       </c>
-      <c r="Y56" s="158" t="n"/>
+      <c r="Y56" s="158" t="n">
+        <v>-200000000</v>
+      </c>
       <c r="Z56" s="158">
         <f>X56*Z$5</f>
         <v/>
@@ -52485,7 +52868,6 @@
       <c r="S72" s="162" t="n"/>
       <c r="X72" s="5" t="n"/>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="5" t="n"/>
@@ -52493,8 +52875,6 @@
       <c r="O74" s="5" t="n"/>
       <c r="X74" s="5" t="n"/>
     </row>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="5" t="n"/>
@@ -52511,8 +52891,6 @@
       <c r="Q77" s="5" t="n"/>
       <c r="X77" s="5" t="n"/>
     </row>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="5" t="n"/>
@@ -56101,7 +56479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A2:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="11.4140625" customWidth="1" min="1" max="1"/>
@@ -56114,7 +56492,6 @@
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="15.5" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="419" t="inlineStr">
@@ -56129,22 +56506,62 @@
       <c r="B3" s="306" t="n"/>
     </row>
     <row r="4" ht="15.5" customHeight="1">
-      <c r="B4" s="344" t="n"/>
+      <c r="B4" s="344" t="inlineStr">
+        <is>
+          <t>1)   What is the corpus requirement to ensure that he is able to sustain the same standard of living for 15 years after retirement?</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16" customHeight="1" thickBot="1">
-      <c r="B5" s="315" t="n"/>
+      <c r="B5" s="315" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="29.5" customHeight="1" thickBot="1">
-      <c r="B6" s="310" t="n"/>
-      <c r="C6" s="311" t="n"/>
-      <c r="D6" s="311" t="n"/>
-      <c r="E6" s="311" t="n"/>
-      <c r="F6" s="311" t="n"/>
+      <c r="B6" s="310" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="C6" s="311" t="inlineStr">
+        <is>
+          <t>Input/Computation</t>
+        </is>
+      </c>
+      <c r="D6" s="311" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E6" s="311" t="inlineStr">
+        <is>
+          <t>Amount (Rs.)</t>
+        </is>
+      </c>
+      <c r="F6" s="311" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" thickBot="1">
-      <c r="B7" s="317" t="n"/>
-      <c r="C7" s="335" t="n"/>
-      <c r="D7" s="335" t="n"/>
+      <c r="B7" s="317" t="inlineStr">
+        <is>
+          <t>Current Age of Mr M</t>
+        </is>
+      </c>
+      <c r="C7" s="335" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D7" s="335" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E7" s="335">
         <f>'1_Personal_Details'!D5</f>
         <v/>
@@ -56152,9 +56569,21 @@
       <c r="F7" s="335" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" thickBot="1">
-      <c r="B8" s="317" t="n"/>
-      <c r="C8" s="335" t="n"/>
-      <c r="D8" s="335" t="n"/>
+      <c r="B8" s="317" t="inlineStr">
+        <is>
+          <t>Retirement Age</t>
+        </is>
+      </c>
+      <c r="C8" s="335" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D8" s="335" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E8" s="503">
         <f>'1_Personal_Details'!H5</f>
         <v/>
@@ -56162,9 +56591,21 @@
       <c r="F8" s="335" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" thickBot="1">
-      <c r="B9" s="317" t="n"/>
-      <c r="C9" s="335" t="n"/>
-      <c r="D9" s="335" t="n"/>
+      <c r="B9" s="317" t="inlineStr">
+        <is>
+          <t>Current Age of Mrs M (Housewife)</t>
+        </is>
+      </c>
+      <c r="C9" s="335" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D9" s="335" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E9" s="335">
         <f>'1_Personal_Details'!D6</f>
         <v/>
@@ -56172,9 +56613,21 @@
       <c r="F9" s="335" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1" thickBot="1">
-      <c r="B10" s="313" t="n"/>
-      <c r="C10" s="146" t="n"/>
-      <c r="D10" s="335" t="n"/>
+      <c r="B10" s="313" t="inlineStr">
+        <is>
+          <t>Time to Retire</t>
+        </is>
+      </c>
+      <c r="C10" s="146" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D10" s="335" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E10" s="335">
         <f>E8-E7</f>
         <v/>
@@ -56189,9 +56642,21 @@
       <c r="F11" s="335" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" thickBot="1">
-      <c r="B12" s="317" t="n"/>
-      <c r="C12" s="335" t="n"/>
-      <c r="D12" s="335" t="n"/>
+      <c r="B12" s="317" t="inlineStr">
+        <is>
+          <t>Life Expectancy of Mr M</t>
+        </is>
+      </c>
+      <c r="C12" s="335" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D12" s="335" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E12" s="335">
         <f>'Assumptions &amp; Computation'!E43</f>
         <v/>
@@ -56199,9 +56664,21 @@
       <c r="F12" s="335" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" thickBot="1">
-      <c r="B13" s="317" t="n"/>
-      <c r="C13" s="335" t="n"/>
-      <c r="D13" s="335" t="n"/>
+      <c r="B13" s="317" t="inlineStr">
+        <is>
+          <t>Life Expectancy of Mrs. M</t>
+        </is>
+      </c>
+      <c r="C13" s="335" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D13" s="335" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E13" s="335">
         <f>'Assumptions &amp; Computation'!E44</f>
         <v/>
@@ -56209,9 +56686,21 @@
       <c r="F13" s="343" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1" thickBot="1">
-      <c r="B14" s="343" t="n"/>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="335" t="n"/>
+      <c r="B14" s="343" t="inlineStr">
+        <is>
+          <t>Age of Mrs M at the time of retirement of Mr M</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D14" s="335" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E14" s="503">
         <f>E8-(E7-E9)</f>
         <v/>
@@ -56219,9 +56708,21 @@
       <c r="F14" s="343" t="n"/>
     </row>
     <row r="15" ht="15.5" customHeight="1">
-      <c r="B15" s="47" t="n"/>
-      <c r="C15" s="47" t="n"/>
-      <c r="D15" s="343" t="n"/>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>No. of Years to be served Post Retirement of Mr M</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D15" s="343" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E15" s="504">
         <f>E13-E14</f>
         <v/>
@@ -56236,9 +56737,21 @@
       <c r="F16" s="335" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" thickBot="1">
-      <c r="B17" s="309" t="n"/>
-      <c r="C17" s="312" t="n"/>
-      <c r="D17" s="312" t="n"/>
+      <c r="B17" s="309" t="inlineStr">
+        <is>
+          <t>Annual Living expenses (at current age)</t>
+        </is>
+      </c>
+      <c r="C17" s="312" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D17" s="312" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="E17" s="328">
         <f>SUM('3_Expenses '!I6:I21)*12</f>
         <v/>
@@ -56246,20 +56759,48 @@
       <c r="F17" s="312" t="n"/>
     </row>
     <row r="18" ht="44" customHeight="1" thickBot="1">
-      <c r="B18" s="309" t="n"/>
-      <c r="C18" s="312" t="n"/>
-      <c r="D18" s="312" t="n"/>
+      <c r="B18" s="309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimated Living Expenses at the time of retirement </t>
+        </is>
+      </c>
+      <c r="C18" s="312" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D18" s="312" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="E18" s="328">
         <f>(SUM('3_Expenses '!I6:I20)-'3_Expenses '!I8)*12</f>
         <v/>
       </c>
-      <c r="F18" s="312" t="n"/>
+      <c r="F18" s="312" t="inlineStr">
+        <is>
+          <t>Exclude school fees etc and add additional medical spend etc</t>
+        </is>
+      </c>
       <c r="G18" s="312" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" thickBot="1">
-      <c r="B19" s="309" t="n"/>
-      <c r="C19" s="312" t="n"/>
-      <c r="D19" s="312" t="n"/>
+      <c r="B19" s="309" t="inlineStr">
+        <is>
+          <t>Current Inflation (given)</t>
+        </is>
+      </c>
+      <c r="C19" s="312" t="inlineStr">
+        <is>
+          <t>Asssumed</t>
+        </is>
+      </c>
+      <c r="D19" s="312" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E19" s="323">
         <f>'Assumptions &amp; Computation'!D3</f>
         <v/>
@@ -56267,9 +56808,21 @@
       <c r="F19" s="322" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1" thickBot="1">
-      <c r="B20" s="309" t="n"/>
-      <c r="C20" s="146" t="n"/>
-      <c r="D20" s="312" t="n"/>
+      <c r="B20" s="309" t="inlineStr">
+        <is>
+          <t>Living expense (at retirement of Mr M.)</t>
+        </is>
+      </c>
+      <c r="C20" s="146" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D20" s="312" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="E20" s="329">
         <f>FV(E19,E10,,-E18)</f>
         <v/>
@@ -56284,9 +56837,21 @@
       <c r="F21" s="505" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" thickBot="1">
-      <c r="B22" s="309" t="n"/>
-      <c r="C22" s="312" t="n"/>
-      <c r="D22" s="312" t="n"/>
+      <c r="B22" s="309" t="inlineStr">
+        <is>
+          <t>Expected return on investment</t>
+        </is>
+      </c>
+      <c r="C22" s="312" t="inlineStr">
+        <is>
+          <t>Asssumed</t>
+        </is>
+      </c>
+      <c r="D22" s="312" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E22" s="506">
         <f>'Assumptions &amp; Computation'!E23</f>
         <v/>
@@ -56294,9 +56859,21 @@
       <c r="F22" s="326" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" thickBot="1">
-      <c r="B23" s="309" t="n"/>
-      <c r="C23" s="312" t="n"/>
-      <c r="D23" s="312" t="n"/>
+      <c r="B23" s="309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expected Inflation post retirement </t>
+        </is>
+      </c>
+      <c r="C23" s="312" t="inlineStr">
+        <is>
+          <t>Asssumed</t>
+        </is>
+      </c>
+      <c r="D23" s="312" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E23" s="506">
         <f>'Assumptions &amp; Computation'!D3</f>
         <v/>
@@ -56304,9 +56881,21 @@
       <c r="F23" s="322" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
-      <c r="B24" s="309" t="n"/>
-      <c r="C24" s="312" t="n"/>
-      <c r="D24" s="312" t="n"/>
+      <c r="B24" s="309" t="inlineStr">
+        <is>
+          <t>Inflation adjusted return (During Retirement years)</t>
+        </is>
+      </c>
+      <c r="C24" s="312" t="inlineStr">
+        <is>
+          <t>Asssumed</t>
+        </is>
+      </c>
+      <c r="D24" s="312" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E24" s="331">
         <f>((1+E22)/(1+E23))-1</f>
         <v/>
@@ -56314,18 +56903,34 @@
       <c r="F24" s="334" t="n"/>
     </row>
     <row r="25" ht="73" customHeight="1" thickBot="1">
-      <c r="B25" s="332" t="n"/>
+      <c r="B25" s="332" t="inlineStr">
+        <is>
+          <t>Retirement corpus required at the time of retirement</t>
+        </is>
+      </c>
       <c r="C25" s="336" t="n"/>
       <c r="D25" s="336" t="n"/>
       <c r="E25" s="333">
         <f>PV(E24,E15,-E20,0,1)</f>
         <v/>
       </c>
-      <c r="F25" s="312" t="n"/>
+      <c r="F25" s="312" t="inlineStr">
+        <is>
+          <t>1 denotes payment at the beginning of the period - as money need to be generated at the beginning of period for spend</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="14.5" customHeight="1">
-      <c r="B26" s="393" t="n"/>
-      <c r="C26" s="394" t="n"/>
+      <c r="B26" s="393" t="inlineStr">
+        <is>
+          <t>One Time Spend Post Retirement</t>
+        </is>
+      </c>
+      <c r="C26" s="394" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
       <c r="D26" s="394" t="n"/>
       <c r="E26" s="395">
         <f>'10_Financial_Goals'!E20</f>
@@ -56335,9 +56940,21 @@
       <c r="G26" s="397" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1">
-      <c r="B27" s="398" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="387" t="n"/>
+      <c r="B27" s="398" t="inlineStr">
+        <is>
+          <t>Time for above spend</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Check Period</t>
+        </is>
+      </c>
+      <c r="D27" s="387" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
       <c r="E27" s="507">
         <f>'10_Financial_Goals'!D20</f>
         <v/>
@@ -56346,9 +56963,21 @@
       <c r="G27" s="399" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B28" s="400" t="n"/>
-      <c r="C28" s="312" t="n"/>
-      <c r="D28" s="312" t="n"/>
+      <c r="B28" s="400" t="inlineStr">
+        <is>
+          <t>Current Inflation (given)</t>
+        </is>
+      </c>
+      <c r="C28" s="312" t="inlineStr">
+        <is>
+          <t>Asssumed</t>
+        </is>
+      </c>
+      <c r="D28" s="312" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E28" s="389">
         <f>E19</f>
         <v/>
@@ -56357,7 +56986,11 @@
       <c r="G28" s="399" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1">
-      <c r="B29" s="401" t="n"/>
+      <c r="B29" s="401" t="inlineStr">
+        <is>
+          <t>Value on the date of retirement</t>
+        </is>
+      </c>
       <c r="C29" s="390" t="n"/>
       <c r="D29" s="391" t="n"/>
       <c r="E29" s="508">
@@ -56368,7 +57001,11 @@
       <c r="G29" s="402" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" thickBot="1">
-      <c r="B30" s="403" t="n"/>
+      <c r="B30" s="403" t="inlineStr">
+        <is>
+          <t>Total Retirement Corpus Needed for Retirement spend and one time goal post retirment</t>
+        </is>
+      </c>
       <c r="C30" s="404" t="n"/>
       <c r="D30" s="404" t="n"/>
       <c r="E30" s="405">
@@ -56386,15 +57023,34 @@
       <c r="A32" s="22" t="n"/>
       <c r="B32" s="306" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
-      <c r="B34" s="445" t="n"/>
-      <c r="C34" s="446" t="n"/>
-      <c r="D34" s="446" t="n"/>
-      <c r="E34" s="446" t="n"/>
+      <c r="B34" s="445" t="inlineStr">
+        <is>
+          <t>2. Computation of additional investments to be done to meet shortfall of Corpus</t>
+        </is>
+      </c>
+      <c r="C34" s="446" t="inlineStr">
+        <is>
+          <t>Recurring Spend Plan</t>
+        </is>
+      </c>
+      <c r="D34" s="446" t="inlineStr">
+        <is>
+          <t>One Time Spend Plan</t>
+        </is>
+      </c>
+      <c r="E34" s="446" t="inlineStr">
+        <is>
+          <t>Total SIP Needs</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
-      <c r="B35" s="447" t="n"/>
+      <c r="B35" s="447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. In this case Corpus needed for retirement </t>
+        </is>
+      </c>
       <c r="C35" s="448">
         <f>E25</f>
         <v/>
@@ -56406,16 +57062,26 @@
       <c r="E35" s="448" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="103" t="n"/>
+      <c r="B36" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projected Corpus based on his current value of investments </t>
+        </is>
+      </c>
       <c r="C36" s="448">
         <f>'10_Financial_Goals'!Y21</f>
         <v/>
       </c>
-      <c r="D36" s="448" t="n"/>
+      <c r="D36" s="448" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="448" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="103" t="n"/>
+      <c r="B37" s="103" t="inlineStr">
+        <is>
+          <t>Shortfall in corpus</t>
+        </is>
+      </c>
       <c r="C37" s="448">
         <f>C35-C36</f>
         <v/>
@@ -56433,7 +57099,11 @@
       <c r="E38" s="448" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="103" t="n"/>
+      <c r="B39" s="103" t="inlineStr">
+        <is>
+          <t>Years to retire</t>
+        </is>
+      </c>
       <c r="C39" s="449">
         <f>'10_Financial_Goals'!D19</f>
         <v/>
@@ -56445,7 +57115,11 @@
       <c r="E39" s="448" t="n"/>
     </row>
     <row r="40" ht="14.5" customHeight="1">
-      <c r="B40" s="450" t="n"/>
+      <c r="B40" s="450" t="inlineStr">
+        <is>
+          <t>Expected return on investment (Post Tax)</t>
+        </is>
+      </c>
       <c r="C40" s="448">
         <f>'Assumptions &amp; Computation'!E22</f>
         <v/>
@@ -56457,7 +57131,11 @@
       <c r="E40" s="448" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="32" t="n"/>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>Additional monthly investments to be done</t>
+        </is>
+      </c>
       <c r="C41" s="440">
         <f>PMT(C40/12,C39*12,0,-C37)</f>
         <v/>
@@ -56470,7 +57148,11 @@
         <f>SUM(C41:D41)</f>
         <v/>
       </c>
-      <c r="F41" s="22" t="n"/>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>This has one goal due in 20 years and other goal due in 24 years</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
       <c r="A42" s="22" t="n"/>
@@ -56481,7 +57163,11 @@
     </row>
     <row r="43" ht="15.5" customHeight="1">
       <c r="A43" s="22" t="n"/>
-      <c r="B43" s="451" t="n"/>
+      <c r="B43" s="451" t="inlineStr">
+        <is>
+          <t>Less SIPs ongoing</t>
+        </is>
+      </c>
       <c r="C43" s="448" t="n"/>
       <c r="D43" s="448" t="n"/>
       <c r="E43" s="448">
@@ -56491,7 +57177,11 @@
     </row>
     <row r="44" ht="15.5" customHeight="1">
       <c r="A44" s="22" t="n"/>
-      <c r="B44" s="452" t="n"/>
+      <c r="B44" s="452" t="inlineStr">
+        <is>
+          <t>Additional SIPs needed to reach goals</t>
+        </is>
+      </c>
       <c r="C44" s="257" t="n"/>
       <c r="D44" s="257" t="n"/>
       <c r="E44" s="440">
@@ -56511,38 +57201,95 @@
     </row>
     <row r="47">
       <c r="A47" s="22" t="n"/>
-      <c r="B47" s="296" t="n"/>
+      <c r="B47" s="296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stepping up investments </t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="B48" s="22" t="n"/>
-    </row>
-    <row r="49"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Stepping up of investments each year can help to start SIP with lower value. Also it helps to reach corpus creation at faster manner</t>
+        </is>
+      </c>
+    </row>
     <row r="50" ht="15.5" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
         <is>
           <t>Increase p.a</t>
         </is>
       </c>
-      <c r="B50" s="345" t="n"/>
+      <c r="B50" s="345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.      Total Retirement Corpus Calculation (If Step up investments are considered) </t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="B51" s="412" t="n"/>
-      <c r="F51" s="435" t="n"/>
+      <c r="B51" s="412" t="inlineStr">
+        <is>
+          <t>Suppose client has limitation on annual contribution, then we need to model how much step up can help him reach his goals</t>
+        </is>
+      </c>
+      <c r="F51" s="435" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="B52" s="51" t="n"/>
-      <c r="C52" s="436" t="n"/>
-      <c r="D52" s="437" t="n"/>
-      <c r="E52" s="437" t="n"/>
-      <c r="F52" s="437" t="n"/>
-      <c r="G52" s="438" t="n"/>
-      <c r="H52" s="436" t="n"/>
-      <c r="I52" s="437" t="n"/>
-      <c r="J52" s="437" t="n"/>
-      <c r="K52" s="32" t="n"/>
+      <c r="C52" s="436" t="inlineStr">
+        <is>
+          <t>Years to retire</t>
+        </is>
+      </c>
+      <c r="D52" s="437" t="inlineStr">
+        <is>
+          <t>Age of Mr. M</t>
+        </is>
+      </c>
+      <c r="E52" s="437" t="inlineStr">
+        <is>
+          <t>Annual Retirement Contribution</t>
+        </is>
+      </c>
+      <c r="F52" s="437" t="inlineStr">
+        <is>
+          <t>Step up increase in Annual Contribution</t>
+        </is>
+      </c>
+      <c r="G52" s="438" t="inlineStr">
+        <is>
+          <t>Total Annual Contribution</t>
+        </is>
+      </c>
+      <c r="H52" s="436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current Corpus (Allocated for retirement) </t>
+        </is>
+      </c>
+      <c r="I52" s="437" t="inlineStr">
+        <is>
+          <t>Rate p.a.</t>
+        </is>
+      </c>
+      <c r="J52" s="437" t="inlineStr">
+        <is>
+          <t>Future Value at age 60</t>
+        </is>
+      </c>
+      <c r="K52" s="32" t="inlineStr">
+        <is>
+          <t>Cumulative FV</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="B53" s="32" t="n"/>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>One Time corpus to FV on date of Retirement</t>
+        </is>
+      </c>
       <c r="C53" s="257">
         <f>'1_Personal_Details'!H5-'1_Personal_Details'!D5</f>
         <v/>
@@ -56572,7 +57319,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="32" t="n"/>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>Annual Contribution to FV on date of retirement</t>
+        </is>
+      </c>
       <c r="C54" s="257">
         <f>C53</f>
         <v/>
@@ -57319,7 +58070,11 @@
       <c r="E76" s="51" t="n"/>
       <c r="F76" s="51" t="n"/>
       <c r="G76" s="51" t="n"/>
-      <c r="H76" s="32" t="n"/>
+      <c r="H76" s="32" t="inlineStr">
+        <is>
+          <t>Retirement Corpus Needed</t>
+        </is>
+      </c>
       <c r="I76" s="51" t="n"/>
       <c r="J76" s="51" t="n"/>
       <c r="K76" s="172">
@@ -57334,7 +58089,11 @@
       <c r="E77" s="51" t="n"/>
       <c r="F77" s="51" t="n"/>
       <c r="G77" s="51" t="n"/>
-      <c r="H77" s="32" t="n"/>
+      <c r="H77" s="32" t="inlineStr">
+        <is>
+          <t>Excess/Gap in Retirement Corpus</t>
+        </is>
+      </c>
       <c r="I77" s="51" t="n"/>
       <c r="J77" s="51" t="n"/>
       <c r="K77" s="172">
@@ -57382,100 +58141,248 @@
       <c r="C82" s="152" t="n"/>
       <c r="D82" s="152" t="n"/>
     </row>
-    <row r="83"/>
     <row r="84">
-      <c r="B84" s="296" t="n"/>
+      <c r="B84" s="296" t="inlineStr">
+        <is>
+          <t>Accumulation Products</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="B85" s="22" t="n"/>
-    </row>
-    <row r="86"/>
-    <row r="87"/>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>PFs, Pension Funds, Mutual Funds etc</t>
+        </is>
+      </c>
+    </row>
     <row r="88">
-      <c r="B88" s="296" t="n"/>
+      <c r="B88" s="296" t="inlineStr">
+        <is>
+          <t>Distribution Products</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="B89" s="22" t="n"/>
-    </row>
-    <row r="90"/>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annuity from Pensions, SWP from MF (beneficial as no tax is there on capital withdrawl portion) </t>
+        </is>
+      </c>
+    </row>
     <row r="91" ht="14.5" customHeight="1" thickBot="1"/>
     <row r="92" ht="41" customHeight="1" thickBot="1">
-      <c r="B92" s="129" t="n"/>
-      <c r="C92" s="129" t="n"/>
-      <c r="D92" s="129" t="n"/>
-      <c r="E92" s="129" t="n"/>
-      <c r="F92" s="434" t="n"/>
+      <c r="B92" s="129" t="inlineStr">
+        <is>
+          <t>Estimate of Retirement Expenses</t>
+        </is>
+      </c>
+      <c r="C92" s="129" t="inlineStr">
+        <is>
+          <t>Retirement Expenses</t>
+        </is>
+      </c>
+      <c r="D92" s="129" t="inlineStr">
+        <is>
+          <t>Retirement Expenses</t>
+        </is>
+      </c>
+      <c r="E92" s="129" t="inlineStr">
+        <is>
+          <t>Retirement Expenses</t>
+        </is>
+      </c>
+      <c r="F92" s="434" t="inlineStr">
+        <is>
+          <t>Sample format for estimating retirement expenses</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="16" customHeight="1" thickBot="1">
-      <c r="B93" s="472" t="n"/>
-      <c r="C93" s="131" t="n"/>
-      <c r="D93" s="132" t="n"/>
+      <c r="B93" s="472" t="inlineStr">
+        <is>
+          <t>Current monthly expenditure</t>
+        </is>
+      </c>
+      <c r="C93" s="131" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D93" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E93" s="132" t="n"/>
     </row>
     <row r="94" ht="16" customHeight="1" thickBot="1">
-      <c r="B94" s="472" t="n"/>
-      <c r="C94" s="131" t="n"/>
-      <c r="D94" s="132" t="n"/>
+      <c r="B94" s="472" t="inlineStr">
+        <is>
+          <t>Additional monthly expenditure (health / misc.)</t>
+        </is>
+      </c>
+      <c r="C94" s="131" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D94" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E94" s="132" t="n"/>
     </row>
     <row r="95" ht="16" customHeight="1" thickBot="1">
-      <c r="B95" s="472" t="n"/>
-      <c r="C95" s="132" t="n"/>
-      <c r="D95" s="132" t="n"/>
+      <c r="B95" s="472" t="inlineStr">
+        <is>
+          <t>Expected general inflation upto age of retirement</t>
+        </is>
+      </c>
+      <c r="C95" s="132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D95" s="132" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E95" s="133" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1" thickBot="1">
-      <c r="B96" s="472" t="n"/>
-      <c r="C96" s="132" t="n"/>
-      <c r="D96" s="132" t="n"/>
+      <c r="B96" s="472" t="inlineStr">
+        <is>
+          <t>Expected health inflation upto age of retirement</t>
+        </is>
+      </c>
+      <c r="C96" s="132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D96" s="132" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E96" s="133" t="n"/>
     </row>
     <row r="97" ht="16" customHeight="1" thickBot="1">
-      <c r="B97" s="472" t="n"/>
+      <c r="B97" s="472" t="inlineStr">
+        <is>
+          <t>Monthly general expenditure at retirement age</t>
+        </is>
+      </c>
       <c r="C97" s="131" t="n"/>
-      <c r="D97" s="132" t="n"/>
+      <c r="D97" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E97" s="132" t="n"/>
     </row>
     <row r="98" ht="16" customHeight="1" thickBot="1">
-      <c r="B98" s="472" t="n"/>
+      <c r="B98" s="472" t="inlineStr">
+        <is>
+          <t>Additional Monthly health expenditure at retirement age</t>
+        </is>
+      </c>
       <c r="C98" s="131" t="n"/>
-      <c r="D98" s="132" t="n"/>
+      <c r="D98" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E98" s="132" t="n"/>
     </row>
     <row r="99" ht="16" customHeight="1" thickBot="1">
-      <c r="B99" s="472" t="n"/>
+      <c r="B99" s="472" t="inlineStr">
+        <is>
+          <t>Total monthly expenditure at retirement age</t>
+        </is>
+      </c>
       <c r="C99" s="131" t="n"/>
-      <c r="D99" s="132" t="n"/>
+      <c r="D99" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E99" s="134" t="n"/>
     </row>
     <row r="100" ht="31.5" customHeight="1" thickBot="1">
-      <c r="B100" s="472" t="n"/>
-      <c r="C100" s="132" t="n"/>
-      <c r="D100" s="132" t="n"/>
+      <c r="B100" s="472" t="inlineStr">
+        <is>
+          <t>Any other monthly income available post retirement</t>
+        </is>
+      </c>
+      <c r="C100" s="132" t="inlineStr">
+        <is>
+          <t>Business Income</t>
+        </is>
+      </c>
+      <c r="D100" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E100" s="131" t="n"/>
     </row>
     <row r="101" ht="16" customHeight="1" thickBot="1">
-      <c r="B101" s="472" t="n"/>
+      <c r="B101" s="472" t="inlineStr">
+        <is>
+          <t>Reduction due to maintenance and taxes</t>
+        </is>
+      </c>
       <c r="C101" s="131" t="n"/>
-      <c r="D101" s="132" t="n"/>
+      <c r="D101" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E101" s="132" t="n"/>
     </row>
     <row r="102" ht="16" customHeight="1" thickBot="1">
-      <c r="B102" s="472" t="n"/>
+      <c r="B102" s="472" t="inlineStr">
+        <is>
+          <t>Monthly Income (if any) at the time of retirement</t>
+        </is>
+      </c>
       <c r="C102" s="131" t="n"/>
-      <c r="D102" s="132" t="n"/>
+      <c r="D102" s="132" t="inlineStr">
+        <is>
+          <t>Rs.</t>
+        </is>
+      </c>
       <c r="E102" s="132" t="n"/>
     </row>
     <row r="103" ht="16" customHeight="1" thickBot="1">
-      <c r="B103" s="472" t="n"/>
+      <c r="B103" s="472" t="inlineStr">
+        <is>
+          <t>Total yearly outflow at retirement age</t>
+        </is>
+      </c>
       <c r="C103" s="135" t="n"/>
-      <c r="D103" s="132" t="n"/>
+      <c r="D103" s="132" t="inlineStr">
+        <is>
+          <t>Rs. (Lacs)</t>
+        </is>
+      </c>
       <c r="E103" s="136" t="n"/>
     </row>
     <row r="104" ht="16" customHeight="1" thickBot="1">
-      <c r="B104" s="137" t="n"/>
+      <c r="B104" s="137" t="inlineStr">
+        <is>
+          <t>Fund required at the time of Retirement</t>
+        </is>
+      </c>
       <c r="C104" s="138" t="n"/>
-      <c r="D104" s="139" t="n"/>
+      <c r="D104" s="139" t="inlineStr">
+        <is>
+          <t>Rs. (Lacs)</t>
+        </is>
+      </c>
       <c r="E104" s="511" t="n"/>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -57485,33 +58392,85 @@
       <c r="E105" s="142" t="n"/>
     </row>
     <row r="106" ht="16" customHeight="1" thickBot="1">
-      <c r="B106" s="470" t="n"/>
+      <c r="B106" s="470" t="inlineStr">
+        <is>
+          <t>Adjusting that with available asset allocation</t>
+        </is>
+      </c>
       <c r="C106" s="512" t="n"/>
       <c r="D106" s="512" t="n"/>
       <c r="E106" s="512" t="n"/>
     </row>
     <row r="107" ht="16" customHeight="1" thickBot="1">
-      <c r="B107" s="472" t="n"/>
-      <c r="C107" s="132" t="n"/>
-      <c r="D107" s="132" t="n"/>
+      <c r="B107" s="472" t="inlineStr">
+        <is>
+          <t>Current yearly investment in EPF &amp; NPS</t>
+        </is>
+      </c>
+      <c r="C107" s="132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D107" s="132" t="inlineStr">
+        <is>
+          <t>Rs. (Lacs)</t>
+        </is>
+      </c>
       <c r="E107" s="132" t="n"/>
     </row>
     <row r="108" ht="16" customHeight="1" thickBot="1">
-      <c r="B108" s="472" t="n"/>
-      <c r="C108" s="132" t="n"/>
-      <c r="D108" s="132" t="n"/>
+      <c r="B108" s="472" t="inlineStr">
+        <is>
+          <t>Yearly increase in EPF &amp; NPS</t>
+        </is>
+      </c>
+      <c r="C108" s="132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D108" s="132" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E108" s="143" t="n"/>
     </row>
     <row r="109" ht="16" customHeight="1" thickBot="1">
-      <c r="B109" s="472" t="n"/>
-      <c r="C109" s="132" t="n"/>
-      <c r="D109" s="132" t="n"/>
+      <c r="B109" s="472" t="inlineStr">
+        <is>
+          <t>Interest rate on EPF &amp; NPS</t>
+        </is>
+      </c>
+      <c r="C109" s="132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D109" s="132" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E109" s="143" t="n"/>
     </row>
     <row r="110" ht="16" customHeight="1" thickBot="1">
-      <c r="B110" s="472" t="n"/>
-      <c r="C110" s="132" t="n"/>
-      <c r="D110" s="132" t="n"/>
+      <c r="B110" s="472" t="inlineStr">
+        <is>
+          <t>Future value of EPF &amp; NPS at the time of retirement</t>
+        </is>
+      </c>
+      <c r="C110" s="132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D110" s="132" t="inlineStr">
+        <is>
+          <t>Rs. (Lacs)</t>
+        </is>
+      </c>
       <c r="E110" s="513" t="n"/>
       <c r="F110" s="486">
         <f>FV(8%,19,-E107,0)</f>
@@ -57519,27 +58478,55 @@
       </c>
     </row>
     <row r="111" ht="15.5" customHeight="1">
-      <c r="B111" s="514" t="n"/>
+      <c r="B111" s="514" t="inlineStr">
+        <is>
+          <t>Current fund in EPF &amp; any other asset allocated for Retirement goal</t>
+        </is>
+      </c>
       <c r="C111" s="146" t="n"/>
       <c r="D111" s="146" t="n"/>
       <c r="E111" s="146" t="n"/>
     </row>
     <row r="112" ht="16" customHeight="1" thickBot="1">
       <c r="B112" s="515" t="n"/>
-      <c r="C112" s="132" t="n"/>
-      <c r="D112" s="132" t="n"/>
+      <c r="C112" s="132" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D112" s="132" t="inlineStr">
+        <is>
+          <t>Rs. (Lacs)</t>
+        </is>
+      </c>
       <c r="E112" s="516" t="n"/>
     </row>
     <row r="113" ht="16" customHeight="1" thickBot="1">
-      <c r="B113" s="472" t="n"/>
+      <c r="B113" s="472" t="inlineStr">
+        <is>
+          <t>Future value EPF &amp; asset allocated for Retirement</t>
+        </is>
+      </c>
       <c r="C113" s="131" t="n"/>
-      <c r="D113" s="132" t="n"/>
+      <c r="D113" s="132" t="inlineStr">
+        <is>
+          <t>Rs. (Lacs)</t>
+        </is>
+      </c>
       <c r="E113" s="513" t="n"/>
     </row>
     <row r="114" ht="16" customHeight="1" thickBot="1">
-      <c r="B114" s="137" t="n"/>
+      <c r="B114" s="137" t="inlineStr">
+        <is>
+          <t>Amount required after adjustment</t>
+        </is>
+      </c>
       <c r="C114" s="138" t="n"/>
-      <c r="D114" s="139" t="n"/>
+      <c r="D114" s="139" t="inlineStr">
+        <is>
+          <t>Rs. (Lacs)</t>
+        </is>
+      </c>
       <c r="E114" s="511" t="n"/>
     </row>
     <row r="115" ht="15.5" customHeight="1">
@@ -57549,19 +58536,24 @@
       <c r="E115" s="142" t="n"/>
     </row>
     <row r="116" ht="15.5" customHeight="1">
-      <c r="B116" s="148" t="n"/>
+      <c r="B116" s="148" t="inlineStr">
+        <is>
+          <t>Monthly EMI needed to reach goals</t>
+        </is>
+      </c>
       <c r="C116" s="148" t="n"/>
       <c r="D116" s="148" t="n"/>
       <c r="E116" s="517" t="n"/>
     </row>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120">
       <c r="F120" s="153" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="154" t="n"/>
+      <c r="B121" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note : Apartment can be used as reversed mortgage (In case of further fund needed post age of 60) </t>
+        </is>
+      </c>
       <c r="C121" s="151" t="n"/>
     </row>
   </sheetData>

--- a/backend_py/stackwealth/excel_engine/master/cfp_master.xlsx
+++ b/backend_py/stackwealth/excel_engine/master/cfp_master.xlsx
@@ -2913,7 +2913,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-IN"/>
         </a:p>
@@ -3712,7 +3712,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3774,7 +3774,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3812,7 +3812,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -3848,7 +3848,7 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3879,7 +3879,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4998,7 +4998,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -5060,7 +5060,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -5098,7 +5098,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -5734,10 +5734,7 @@
         <v/>
       </c>
       <c r="L3" s="520" t="n"/>
-      <c r="M3" s="519">
-        <f>839368</f>
-        <v/>
-      </c>
+      <c r="M3" s="519" t="n"/>
       <c r="N3" s="167" t="n"/>
       <c r="O3" s="51" t="n"/>
       <c r="P3" s="167" t="n"/>
@@ -6165,10 +6162,7 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="92" t="n"/>
       <c r="D10" s="92" t="n"/>
-      <c r="E10" s="8">
-        <f>15000000*0</f>
-        <v/>
-      </c>
+      <c r="E10" s="8" t="n"/>
       <c r="F10" s="93" t="n"/>
       <c r="G10" s="518">
         <f>'Assumptions &amp; Computation'!D8</f>
@@ -17103,7 +17097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="B3:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="2.4140625" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -17116,8 +17110,6 @@
     <col width="39.58203125" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="C3" s="33" t="n"/>
       <c r="D3" s="33" t="n"/>
@@ -17277,8 +17269,6 @@
       <c r="I13" s="30" t="n"/>
       <c r="J13" s="30" t="n"/>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16" ht="15.5" customHeight="1">
       <c r="C16" s="36" t="n"/>
       <c r="D16" s="37" t="n"/>
@@ -17338,8 +17328,6 @@
       <c r="I20" s="57" t="n"/>
       <c r="J20" s="57" t="n"/>
     </row>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="15.5" customHeight="1">
       <c r="C23" s="36" t="n"/>
       <c r="D23" s="37" t="n"/>
@@ -17529,21 +17517,9 @@
       <c r="I31" s="30" t="n"/>
       <c r="J31" s="30" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="E41" s="5" t="n"/>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="E45" s="5" t="n"/>
     </row>
@@ -17559,7 +17535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="B3:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="2.4140625" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -17572,8 +17548,6 @@
     <col width="39.58203125" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="C3" s="33" t="n"/>
       <c r="D3" s="33" t="n"/>
@@ -17924,21 +17898,6 @@
       <c r="I27" s="30" t="n"/>
       <c r="J27" s="30" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="15.5" customHeight="1">
       <c r="C43" s="46" t="n"/>
       <c r="D43" s="46" t="n"/>
@@ -17989,84 +17948,30 @@
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="2" t="n"/>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="E52" s="5" t="n"/>
     </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="E62" s="5" t="n"/>
     </row>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="E73" s="5" t="n"/>
     </row>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
     <row r="82">
       <c r="E82" s="5" t="n"/>
     </row>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
     <row r="87">
       <c r="E87" s="5" t="n"/>
     </row>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
     <row r="93">
       <c r="E93" s="5" t="n"/>
     </row>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
     <row r="98">
       <c r="E98" s="5" t="n"/>
     </row>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
     <row r="109">
       <c r="E109" s="5" t="n"/>
     </row>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
     <row r="113">
       <c r="E113" s="5" t="n"/>
     </row>
@@ -18082,7 +17987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H999"/>
+  <dimension ref="B1:H999"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -21266,7 +21171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="B1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.9140625" customWidth="1" min="1" max="1"/>
@@ -21546,8 +21451,6 @@
       <c r="J22" s="83" t="n"/>
       <c r="K22" s="78" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="65" t="n"/>
     </row>
@@ -22542,7 +22445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="B1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.9140625" customWidth="1" min="1" max="1"/>
@@ -22816,7 +22719,6 @@
       <c r="H24" s="75" t="n"/>
       <c r="I24" s="75" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="15" customHeight="1">
       <c r="E26" s="150">
         <f>SUMIF(F$2:F$23,F26,E$2:E$23)</f>
@@ -23896,10 +23798,7 @@
       <c r="B8" s="66" t="n"/>
       <c r="C8" s="66" t="n"/>
       <c r="D8" s="362" t="n"/>
-      <c r="E8" s="106">
-        <f>400000/2</f>
-        <v/>
-      </c>
+      <c r="E8" s="106" t="n"/>
       <c r="F8" s="109" t="n"/>
       <c r="G8" s="51" t="n"/>
     </row>
@@ -27900,7 +27799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1002"/>
+  <dimension ref="B1:D1002"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.83203125" customWidth="1" min="1" max="1"/>
@@ -30977,7 +30876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="B1:F1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.83203125" customWidth="1" min="1" max="1"/>
@@ -36318,7 +36217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="B1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -37390,7 +37289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1001"/>
+  <dimension ref="B1:D1001"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.9140625" customWidth="1" min="1" max="1"/>
@@ -40459,7 +40358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G997"/>
+  <dimension ref="B1:G997"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.25" customWidth="1" min="1" max="1"/>
@@ -43566,7 +43465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="B1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.75" customWidth="1" min="1" max="1"/>
@@ -46723,14 +46622,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="C2:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="56.1640625" customWidth="1" style="19" min="3" max="3"/>
     <col width="56.1640625" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="C2" s="19" t="inlineStr">
         <is>
@@ -46738,8 +46636,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="11" t="n"/>
@@ -57332,10 +57228,7 @@
         <f>D53</f>
         <v/>
       </c>
-      <c r="E54" s="257">
-        <f>1200000</f>
-        <v/>
-      </c>
+      <c r="E54" s="257" t="n"/>
       <c r="F54" s="257" t="n"/>
       <c r="G54" s="440">
         <f>SUM(E54:F54)</f>

--- a/backend_py/stackwealth/excel_engine/master/cfp_master.xlsx
+++ b/backend_py/stackwealth/excel_engine/master/cfp_master.xlsx
@@ -5715,11 +5715,19 @@
           <t>Car Purchase</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C3" s="92" t="n"/>
       <c r="D3" s="92" t="n"/>
       <c r="E3" s="8" t="n"/>
-      <c r="F3" s="93" t="n"/>
+      <c r="F3" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G3" s="518">
         <f>'Assumptions &amp; Computation'!D3</f>
         <v/>
@@ -5728,12 +5736,20 @@
         <f>FV(G3,D3,,-E3)</f>
         <v/>
       </c>
-      <c r="J3" s="167" t="n"/>
+      <c r="J3" s="167" t="inlineStr">
+        <is>
+          <t>Equity  tagged as weak</t>
+        </is>
+      </c>
       <c r="K3" s="519">
         <f>'4B_Equity_Stocks'!E26</f>
         <v/>
       </c>
-      <c r="L3" s="520" t="n"/>
+      <c r="L3" s="520" t="inlineStr">
+        <is>
+          <t>Fixed Deposits</t>
+        </is>
+      </c>
       <c r="M3" s="519" t="n"/>
       <c r="N3" s="167" t="n"/>
       <c r="O3" s="51" t="n"/>
@@ -5775,11 +5791,19 @@
           <t>Foreign Travel</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Desirable</t>
+        </is>
+      </c>
       <c r="C4" s="92" t="n"/>
       <c r="D4" s="92" t="n"/>
       <c r="E4" s="8" t="n"/>
-      <c r="F4" s="93" t="n"/>
+      <c r="F4" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G4" s="518">
         <f>'Assumptions &amp; Computation'!D3</f>
         <v/>
@@ -5790,17 +5814,29 @@
       </c>
       <c r="J4" s="519" t="n"/>
       <c r="K4" s="519" t="n"/>
-      <c r="L4" s="520" t="n"/>
+      <c r="L4" s="520" t="inlineStr">
+        <is>
+          <t>Fixed Deposits</t>
+        </is>
+      </c>
       <c r="M4" s="519">
         <f>'11. Inc Exp,Networth,Rec Invest'!I30-'10_Financial_Goals'!M3</f>
         <v/>
       </c>
-      <c r="N4" s="167" t="n"/>
+      <c r="N4" s="167" t="inlineStr">
+        <is>
+          <t>Bonds</t>
+        </is>
+      </c>
       <c r="O4" s="51">
         <f>'4C_Fixed_Income'!E3</f>
         <v/>
       </c>
-      <c r="P4" s="167" t="n"/>
+      <c r="P4" s="167" t="inlineStr">
+        <is>
+          <t>Stocks tagged as Neutral</t>
+        </is>
+      </c>
       <c r="Q4" s="519" t="n"/>
       <c r="R4" s="51" t="n"/>
       <c r="S4" s="519" t="n"/>
@@ -5838,11 +5874,19 @@
           <t xml:space="preserve">House Purchase </t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C5" s="92" t="n"/>
       <c r="D5" s="92" t="n"/>
       <c r="E5" s="8" t="n"/>
-      <c r="F5" s="93" t="n"/>
+      <c r="F5" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G5" s="518">
         <f>'Assumptions &amp; Computation'!D8</f>
         <v/>
@@ -5857,17 +5901,29 @@
       <c r="M5" s="51" t="n"/>
       <c r="N5" s="51" t="n"/>
       <c r="O5" s="51" t="n"/>
-      <c r="P5" s="167" t="n"/>
+      <c r="P5" s="167" t="inlineStr">
+        <is>
+          <t>Stocks tagged as Neutral</t>
+        </is>
+      </c>
       <c r="Q5" s="172">
         <f>'4B_Equity_Stocks'!E27-Q4</f>
         <v/>
       </c>
-      <c r="R5" s="32" t="n"/>
+      <c r="R5" s="32" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
       <c r="S5" s="51">
         <f>'4C_Fixed_Income'!E4</f>
         <v/>
       </c>
-      <c r="T5" s="32" t="n"/>
+      <c r="T5" s="32" t="inlineStr">
+        <is>
+          <t>PPF</t>
+        </is>
+      </c>
       <c r="U5" s="51">
         <f>'4C_Fixed_Income'!E5</f>
         <v/>
@@ -5899,7 +5955,11 @@
         <f>AB5-AC5</f>
         <v/>
       </c>
-      <c r="AE5" s="51" t="n"/>
+      <c r="AE5" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Hybrid</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="14.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -5907,11 +5967,19 @@
           <t>Child 1 Education</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C6" s="92" t="n"/>
       <c r="D6" s="92" t="n"/>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="93" t="n"/>
+      <c r="F6" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G6" s="518">
         <f>'Assumptions &amp; Computation'!D4</f>
         <v/>
@@ -5930,7 +5998,11 @@
       <c r="Q6" s="51" t="n"/>
       <c r="R6" s="167" t="n"/>
       <c r="S6" s="485" t="n"/>
-      <c r="T6" s="167" t="n"/>
+      <c r="T6" s="167" t="inlineStr">
+        <is>
+          <t>EPF</t>
+        </is>
+      </c>
       <c r="U6" s="485">
         <f>'11. Inc Exp,Networth,Rec Invest'!I34</f>
         <v/>
@@ -5962,7 +6034,11 @@
         <f>AB6-AC6</f>
         <v/>
       </c>
-      <c r="AE6" s="51" t="n"/>
+      <c r="AE6" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Hybrid</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -5970,11 +6046,19 @@
           <t>Child 2 Education</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C7" s="92" t="n"/>
       <c r="D7" s="92" t="n"/>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="93" t="n"/>
+      <c r="F7" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G7" s="518">
         <f>'Assumptions &amp; Computation'!D4</f>
         <v/>
@@ -5993,12 +6077,20 @@
       <c r="Q7" s="51" t="n"/>
       <c r="R7" s="51" t="n"/>
       <c r="S7" s="51" t="n"/>
-      <c r="T7" s="32" t="n"/>
+      <c r="T7" s="32" t="inlineStr">
+        <is>
+          <t>Equity as Strong</t>
+        </is>
+      </c>
       <c r="U7" s="172">
         <f>'4B_Equity_Stocks'!E28</f>
         <v/>
       </c>
-      <c r="V7" s="413" t="n"/>
+      <c r="V7" s="413" t="inlineStr">
+        <is>
+          <t>Mutual Fund</t>
+        </is>
+      </c>
       <c r="W7" s="157">
         <f>'11. Inc Exp,Networth,Rec Invest'!I28</f>
         <v/>
@@ -6028,7 +6120,11 @@
         <f>AB7-AC7</f>
         <v/>
       </c>
-      <c r="AE7" s="51" t="n"/>
+      <c r="AE7" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="14.5" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -6036,11 +6132,19 @@
           <t>Child 1 Marriage</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C8" s="92" t="n"/>
       <c r="D8" s="92" t="n"/>
       <c r="E8" s="8" t="n"/>
-      <c r="F8" s="93" t="n"/>
+      <c r="F8" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G8" s="518">
         <f>'Assumptions &amp; Computation'!D3</f>
         <v/>
@@ -6091,7 +6195,11 @@
         <f>AB8-AC8</f>
         <v/>
       </c>
-      <c r="AE8" s="51" t="n"/>
+      <c r="AE8" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="14.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -6099,11 +6207,19 @@
           <t>Child 2 Marriage</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C9" s="92" t="n"/>
       <c r="D9" s="92" t="n"/>
       <c r="E9" s="8" t="n"/>
-      <c r="F9" s="93" t="n"/>
+      <c r="F9" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G9" s="518">
         <f>'Assumptions &amp; Computation'!D3</f>
         <v/>
@@ -6151,7 +6267,11 @@
         <f>AB9-AC9</f>
         <v/>
       </c>
-      <c r="AE9" s="51" t="n"/>
+      <c r="AE9" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="14.5" customHeight="1">
       <c r="A10" s="177" t="inlineStr">
@@ -6159,11 +6279,19 @@
           <t>House Purchase 2</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C10" s="92" t="n"/>
       <c r="D10" s="92" t="n"/>
       <c r="E10" s="8" t="n"/>
-      <c r="F10" s="93" t="n"/>
+      <c r="F10" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G10" s="518">
         <f>'Assumptions &amp; Computation'!D8</f>
         <v/>
@@ -6211,7 +6339,11 @@
         <f>AB10-AC10</f>
         <v/>
       </c>
-      <c r="AE10" s="51" t="n"/>
+      <c r="AE10" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="14.5" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -6219,7 +6351,11 @@
           <t>Loan Repayment</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -6264,7 +6400,11 @@
         <f>AB11-AC11</f>
         <v/>
       </c>
-      <c r="AE11" s="51" t="n"/>
+      <c r="AE11" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="14.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -6272,7 +6412,11 @@
           <t>Social Commitments</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Desirable</t>
+        </is>
+      </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
@@ -6317,7 +6461,11 @@
         <f>AB12-AC12</f>
         <v/>
       </c>
-      <c r="AE12" s="51" t="n"/>
+      <c r="AE12" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="C13" s="4" t="n"/>
@@ -6326,7 +6474,11 @@
         <f>SUMIF(F3:F12,F13,E3:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="121" t="n"/>
+      <c r="F13" s="121" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n"/>
       <c r="J13" s="51" t="n"/>
       <c r="K13" s="51" t="n"/>
@@ -6373,7 +6525,11 @@
         <f>SUMIF(F3:F12,F14,E3:E12)</f>
         <v/>
       </c>
-      <c r="F14" s="95" t="n"/>
+      <c r="F14" s="95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual </t>
+        </is>
+      </c>
       <c r="G14" s="4" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="174">
@@ -6466,6 +6622,11 @@
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
       <c r="K16" s="150">
         <f>'4B_Equity_Stocks'!E26-'10_Financial_Goals'!K14</f>
         <v/>
@@ -6513,10 +6674,31 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="Y18" s="22" t="n"/>
-      <c r="Z18" s="22" t="n"/>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Total Current Value of Asset Allocated</t>
+        </is>
+      </c>
+      <c r="Y18" s="22" t="inlineStr">
+        <is>
+          <t>FV of Current Assets on retirement</t>
+        </is>
+      </c>
+      <c r="Z18" s="22" t="inlineStr">
+        <is>
+          <t>Gap in Future Value</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="14.5" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -6524,11 +6706,19 @@
           <t>Retirement Cost</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="442" t="n"/>
       <c r="E19" s="94" t="n"/>
-      <c r="F19" s="95" t="n"/>
+      <c r="F19" s="95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual </t>
+        </is>
+      </c>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="91">
         <f>'Retirement Plan'!E25</f>
@@ -6546,7 +6736,11 @@
         <f>'11. Inc Exp,Networth,Rec Invest'!I35</f>
         <v/>
       </c>
-      <c r="L19" s="32" t="n"/>
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>Post Office Saving A/c</t>
+        </is>
+      </c>
       <c r="M19" s="51">
         <f>'11. Inc Exp,Networth,Rec Invest'!I36</f>
         <v/>
@@ -6595,7 +6789,11 @@
         <f>AB19-AC19</f>
         <v/>
       </c>
-      <c r="AE19" s="51" t="n"/>
+      <c r="AE19" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="14.5" customHeight="1">
       <c r="A20" s="177" t="inlineStr">
@@ -6603,11 +6801,19 @@
           <t>Orphanage</t>
         </is>
       </c>
-      <c r="B20" s="417" t="n"/>
+      <c r="B20" s="417" t="inlineStr">
+        <is>
+          <t>Desirable</t>
+        </is>
+      </c>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="443" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="93" t="n"/>
+      <c r="F20" s="93" t="inlineStr">
+        <is>
+          <t>One Time</t>
+        </is>
+      </c>
       <c r="G20" s="379" t="n"/>
       <c r="H20" s="91">
         <f>'Retirement Plan'!E29</f>
@@ -6659,7 +6865,11 @@
         <f>AB20-AC20</f>
         <v/>
       </c>
-      <c r="AE20" s="51" t="n"/>
+      <c r="AE20" s="51" t="inlineStr">
+        <is>
+          <t>MF SIP : Equity</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="C21" s="4" t="n"/>
@@ -6761,7 +6971,11 @@
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
-      <c r="W24" s="22" t="n"/>
+      <c r="W24" s="22" t="inlineStr">
+        <is>
+          <t>Total Aset Allocated</t>
+        </is>
+      </c>
       <c r="X24" s="152">
         <f>X14+X19</f>
         <v/>
@@ -6778,7 +6992,11 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="W25" s="22" t="n"/>
+      <c r="W25" s="22" t="inlineStr">
+        <is>
+          <t>Total Assets to be allocated</t>
+        </is>
+      </c>
       <c r="X25" s="152">
         <f>'11. Inc Exp,Networth,Rec Invest'!I42</f>
         <v/>
@@ -6790,7 +7008,11 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="W26" s="22" t="n"/>
+      <c r="W26" s="22" t="inlineStr">
+        <is>
+          <t>Under/(Over) Allocation of Assets</t>
+        </is>
+      </c>
       <c r="X26" s="152">
         <f>X25-X24</f>
         <v/>
@@ -6826,7 +7048,11 @@
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
-      <c r="W29" s="22" t="n"/>
+      <c r="W29" s="22" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="C30" s="4" t="n"/>
@@ -6834,7 +7060,11 @@
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
-      <c r="W30" s="22" t="n"/>
+      <c r="W30" s="22" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
       <c r="X30">
         <f>'11. Inc Exp,Networth,Rec Invest'!I44</f>
         <v/>
@@ -7074,7 +7304,11 @@
           <t xml:space="preserve">Goals maturing in next 1 year </t>
         </is>
       </c>
-      <c r="B53" s="305" t="n"/>
+      <c r="B53" s="305" t="inlineStr">
+        <is>
+          <t>Liquid Funds</t>
+        </is>
+      </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
@@ -7086,7 +7320,11 @@
           <t xml:space="preserve">Goals maturing in next 2-3 year </t>
         </is>
       </c>
-      <c r="B54" s="305" t="n"/>
+      <c r="B54" s="305" t="inlineStr">
+        <is>
+          <t>Short to Mid term debt fund</t>
+        </is>
+      </c>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
@@ -7098,7 +7336,11 @@
           <t xml:space="preserve">Goals maturing in next 4-5 year </t>
         </is>
       </c>
-      <c r="B55" s="305" t="n"/>
+      <c r="B55" s="305" t="inlineStr">
+        <is>
+          <t>Hybrid Funds</t>
+        </is>
+      </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
@@ -7110,7 +7352,11 @@
           <t xml:space="preserve">Goals maturing &gt; 5 year </t>
         </is>
       </c>
-      <c r="B56" s="305" t="n"/>
+      <c r="B56" s="305" t="inlineStr">
+        <is>
+          <t>Flexi cap equity fund</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
@@ -13922,20 +14168,76 @@
           <t>Family Details</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="27" t="n"/>
-      <c r="M4" s="27" t="n"/>
-      <c r="N4" s="27" t="n"/>
-      <c r="O4" s="27" t="n"/>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date Of Birth</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Retirement Year</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Marital Status</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>Retirement Age (Planned)</t>
+        </is>
+      </c>
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>Life Expectancy</t>
+        </is>
+      </c>
+      <c r="J4" s="27" t="inlineStr">
+        <is>
+          <t>City &amp; Country of Residence</t>
+        </is>
+      </c>
+      <c r="K4" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Occupation </t>
+        </is>
+      </c>
+      <c r="L4" s="27" t="inlineStr">
+        <is>
+          <t>Name of Organization Where you work?</t>
+        </is>
+      </c>
+      <c r="M4" s="27" t="inlineStr">
+        <is>
+          <t>Smokes?</t>
+        </is>
+      </c>
+      <c r="N4" s="27" t="inlineStr">
+        <is>
+          <t>Any Health Risks</t>
+        </is>
+      </c>
+      <c r="O4" s="27" t="inlineStr">
+        <is>
+          <t>Notes/Remarks/Comments</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -13943,7 +14245,11 @@
           <t>Client Name</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Mr M</t>
+        </is>
+      </c>
       <c r="C5" s="118" t="n"/>
       <c r="D5" s="524">
         <f>(D$3-C5)/365.25</f>
@@ -13953,15 +14259,43 @@
         <f>IF(H5&gt;0,(ROUND($E$2+(H5-D5),0)),"NA")</f>
         <v/>
       </c>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
       <c r="H5" s="24" t="n"/>
       <c r="I5" s="24" t="n"/>
-      <c r="J5" s="24" t="n"/>
-      <c r="K5" s="24" t="n"/>
-      <c r="L5" s="24" t="n"/>
-      <c r="M5" s="24" t="n"/>
-      <c r="N5" s="24" t="n"/>
+      <c r="J5" s="24" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>Salaried</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="inlineStr">
+        <is>
+          <t>Polestar</t>
+        </is>
+      </c>
+      <c r="M5" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="O5" s="24" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -13970,7 +14304,11 @@
           <t>Spouse Name</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Mrs M</t>
+        </is>
+      </c>
       <c r="C6" s="118" t="n"/>
       <c r="D6" s="524">
         <f>(D$3-C6)/365.25</f>
@@ -13980,16 +14318,48 @@
         <f>IF(H6&gt;0,(ROUND($E$2+(H6-D6),0)),"NA")</f>
         <v/>
       </c>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
       <c r="H6" s="24" t="n"/>
       <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="n"/>
-      <c r="K6" s="24" t="n"/>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
-      <c r="O6" s="24" t="n"/>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t>Rental Income From Apartment</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
@@ -13997,7 +14367,11 @@
           <t>Child 1 Name</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n"/>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Daughter of Mrs. M</t>
+        </is>
+      </c>
       <c r="C7" s="118" t="n"/>
       <c r="D7" s="524">
         <f>(D$3-C7)/365.25</f>
@@ -14007,15 +14381,43 @@
         <f>IF(H7&gt;0,(ROUND($E$2+(H7-D7),0)),"NA")</f>
         <v/>
       </c>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="24" t="n"/>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="H7" s="24" t="n"/>
       <c r="I7" s="24" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="24" t="n"/>
+      <c r="J7" s="24" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="M7" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="O7" s="24" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -14024,7 +14426,11 @@
           <t>Child 2 Name</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n"/>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Son of Mrs. M</t>
+        </is>
+      </c>
       <c r="C8" s="118" t="n"/>
       <c r="D8" s="524">
         <f>(D$3-C8)/365.25</f>
@@ -14034,15 +14440,43 @@
         <f>IF(H8&gt;0,(ROUND($E$2+(H8-D8),0)),"NA")</f>
         <v/>
       </c>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="H8" s="24" t="n"/>
       <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="n"/>
-      <c r="K8" s="24" t="n"/>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="24" t="n"/>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Grade Nursery</t>
+        </is>
+      </c>
+      <c r="M8" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="O8" s="24" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -14096,20 +14530,44 @@
           <t>Mother</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n"/>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Mrs Y</t>
+        </is>
+      </c>
       <c r="C11" s="118" t="n"/>
       <c r="D11" s="524">
         <f>(D$3-C11)/365.25</f>
         <v/>
       </c>
       <c r="E11" s="375" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Widow</t>
+        </is>
+      </c>
       <c r="H11" s="24" t="n"/>
       <c r="I11" s="24" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>Housewife</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="M11" s="24" t="n"/>
       <c r="N11" s="24" t="n"/>
       <c r="O11" s="24" t="n"/>
@@ -17113,28 +17571,68 @@
     <row r="3">
       <c r="C3" s="33" t="n"/>
       <c r="D3" s="33" t="n"/>
-      <c r="E3" s="34" t="n"/>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t>Monthly Household Cash Budget - Current</t>
+        </is>
+      </c>
       <c r="F3" s="33" t="n"/>
       <c r="G3" s="33" t="n"/>
       <c r="H3" s="33" t="n"/>
-      <c r="I3" s="34" t="n"/>
+      <c r="I3" s="34" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="J3" s="33" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="35" t="n"/>
       <c r="C4" s="58" t="n"/>
       <c r="D4" s="58" t="n"/>
-      <c r="E4" s="58" t="n"/>
-      <c r="F4" s="58" t="n"/>
-      <c r="G4" s="58" t="n"/>
-      <c r="H4" s="58" t="n"/>
-      <c r="I4" s="58" t="n"/>
-      <c r="J4" s="58" t="n"/>
+      <c r="E4" s="58" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="F4" s="58" t="inlineStr">
+        <is>
+          <t>Mr. X</t>
+        </is>
+      </c>
+      <c r="G4" s="58" t="inlineStr">
+        <is>
+          <t>Mrs. Y</t>
+        </is>
+      </c>
+      <c r="H4" s="58" t="inlineStr">
+        <is>
+          <t>Others /Family</t>
+        </is>
+      </c>
+      <c r="I4" s="58" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J4" s="58" t="inlineStr">
+        <is>
+          <t>Optional Remarks/Comments</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15.5" customHeight="1">
-      <c r="C5" s="36" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D5" s="37" t="n"/>
-      <c r="E5" s="38" t="n"/>
+      <c r="E5" s="38" t="inlineStr">
+        <is>
+          <t>Income (Money Inflows)</t>
+        </is>
+      </c>
       <c r="F5" s="37" t="n"/>
       <c r="G5" s="37" t="n"/>
       <c r="H5" s="37" t="n"/>
@@ -17144,7 +17642,11 @@
     <row r="6" ht="15.5" customHeight="1">
       <c r="C6" s="28" t="n"/>
       <c r="D6" s="28" t="n"/>
-      <c r="E6" s="29" t="n"/>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>Gross Salary per month</t>
+        </is>
+      </c>
       <c r="F6" s="31" t="n"/>
       <c r="G6" s="31" t="n"/>
       <c r="H6" s="31" t="n"/>
@@ -17160,7 +17662,11 @@
         <f>D6+1</f>
         <v/>
       </c>
-      <c r="E7" s="29" t="n"/>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Business Income (Net)</t>
+        </is>
+      </c>
       <c r="F7" s="31" t="n"/>
       <c r="G7" s="31" t="n"/>
       <c r="H7" s="31" t="n"/>
@@ -17176,7 +17682,11 @@
         <f>D7+1</f>
         <v/>
       </c>
-      <c r="E8" s="29" t="n"/>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
       <c r="F8" s="31" t="n"/>
       <c r="G8" s="31" t="n"/>
       <c r="H8" s="31">
@@ -17195,7 +17705,11 @@
         <f>D8+1</f>
         <v/>
       </c>
-      <c r="E9" s="29" t="n"/>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Income from Investment</t>
+        </is>
+      </c>
       <c r="F9" s="31" t="n"/>
       <c r="G9" s="31" t="n"/>
       <c r="H9" s="31" t="n"/>
@@ -17211,7 +17725,11 @@
         <f>D9+1</f>
         <v/>
       </c>
-      <c r="E10" s="29" t="n"/>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Income 1 (Please Specify) </t>
+        </is>
+      </c>
       <c r="F10" s="31" t="n"/>
       <c r="G10" s="31" t="n"/>
       <c r="H10" s="31" t="n"/>
@@ -17227,7 +17745,11 @@
         <f>D10+1</f>
         <v/>
       </c>
-      <c r="E11" s="29" t="n"/>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Income 1 (Please Specify) </t>
+        </is>
+      </c>
       <c r="F11" s="31" t="n"/>
       <c r="G11" s="31" t="n"/>
       <c r="H11" s="31" t="n"/>
@@ -17240,7 +17762,11 @@
     <row r="12" ht="15.5" customHeight="1">
       <c r="C12" s="39" t="n"/>
       <c r="D12" s="39" t="n"/>
-      <c r="E12" s="40" t="n"/>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>Total Gross Income</t>
+        </is>
+      </c>
       <c r="F12" s="41">
         <f>SUM(F6:F11)</f>
         <v/>
@@ -17270,9 +17796,17 @@
       <c r="J13" s="30" t="n"/>
     </row>
     <row r="16" ht="15.5" customHeight="1">
-      <c r="C16" s="36" t="n"/>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
       <c r="D16" s="37" t="n"/>
-      <c r="E16" s="38" t="n"/>
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>Deductions (Mandatory Cash Outflow)</t>
+        </is>
+      </c>
       <c r="F16" s="42" t="n"/>
       <c r="G16" s="42" t="n"/>
       <c r="H16" s="42" t="n"/>
@@ -17282,7 +17816,11 @@
     <row r="17" ht="15.5" customHeight="1">
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="28" t="n"/>
-      <c r="E17" s="29" t="n"/>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Taxes from Salary</t>
+        </is>
+      </c>
       <c r="F17" s="31" t="n"/>
       <c r="G17" s="31" t="n"/>
       <c r="H17" s="31" t="n"/>
@@ -17298,7 +17836,11 @@
         <f>+D17+1</f>
         <v/>
       </c>
-      <c r="E18" s="29" t="n"/>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t>Contribution to Provident Fund</t>
+        </is>
+      </c>
       <c r="F18" s="31" t="n"/>
       <c r="G18" s="31" t="n"/>
       <c r="H18" s="31" t="n"/>
@@ -17311,7 +17853,11 @@
     <row r="19" ht="15.5" customHeight="1">
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
-      <c r="E19" s="29" t="n"/>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>Other Taxes &amp; Deductions (Pls Specify)</t>
+        </is>
+      </c>
       <c r="F19" s="31" t="n"/>
       <c r="G19" s="31" t="n"/>
       <c r="H19" s="31" t="n"/>
@@ -17329,9 +17875,17 @@
       <c r="J20" s="57" t="n"/>
     </row>
     <row r="23" ht="15.5" customHeight="1">
-      <c r="C23" s="36" t="n"/>
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
       <c r="D23" s="37" t="n"/>
-      <c r="E23" s="38" t="n"/>
+      <c r="E23" s="38" t="inlineStr">
+        <is>
+          <t>NET INCOME</t>
+        </is>
+      </c>
       <c r="F23" s="42" t="n"/>
       <c r="G23" s="42" t="n"/>
       <c r="H23" s="42" t="n"/>
@@ -17341,7 +17895,11 @@
     <row r="24" ht="15.5" customHeight="1">
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
-      <c r="E24" s="29" t="n"/>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>Net Salary per month</t>
+        </is>
+      </c>
       <c r="F24" s="31">
         <f>F6-F17-F18</f>
         <v/>
@@ -17366,7 +17924,11 @@
         <f>D24+1</f>
         <v/>
       </c>
-      <c r="E25" s="29" t="n"/>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>Business Income</t>
+        </is>
+      </c>
       <c r="F25" s="31">
         <f>F7</f>
         <v/>
@@ -17391,7 +17953,11 @@
         <f>D25+1</f>
         <v/>
       </c>
-      <c r="E26" s="29" t="n"/>
+      <c r="E26" s="29" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
       <c r="F26" s="31">
         <f>F8</f>
         <v/>
@@ -17416,7 +17982,11 @@
         <f>D26+1</f>
         <v/>
       </c>
-      <c r="E27" s="29" t="n"/>
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>Income from Investment</t>
+        </is>
+      </c>
       <c r="F27" s="31">
         <f>F9</f>
         <v/>
@@ -17441,7 +18011,11 @@
         <f>D27+1</f>
         <v/>
       </c>
-      <c r="E28" s="29" t="n"/>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Income 1 (Please Specify) </t>
+        </is>
+      </c>
       <c r="F28" s="31">
         <f>F10</f>
         <v/>
@@ -17466,7 +18040,11 @@
         <f>D28+1</f>
         <v/>
       </c>
-      <c r="E29" s="29" t="n"/>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other Income 1 (Please Specify) </t>
+        </is>
+      </c>
       <c r="F29" s="31">
         <f>F11</f>
         <v/>
@@ -17488,7 +18066,11 @@
     <row r="30" ht="15.5" customHeight="1">
       <c r="C30" s="39" t="n"/>
       <c r="D30" s="39" t="n"/>
-      <c r="E30" s="40" t="n"/>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total Income </t>
+        </is>
+      </c>
       <c r="F30" s="41">
         <f>SUM(F24:F29)</f>
         <v/>
@@ -17551,28 +18133,64 @@
     <row r="3">
       <c r="C3" s="33" t="n"/>
       <c r="D3" s="33" t="n"/>
-      <c r="E3" s="34" t="n"/>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expense Details - Momthly </t>
+        </is>
+      </c>
       <c r="F3" s="33" t="n"/>
       <c r="G3" s="33" t="n"/>
       <c r="H3" s="33" t="n"/>
-      <c r="I3" s="34" t="n"/>
+      <c r="I3" s="34" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="J3" s="33" t="n"/>
     </row>
     <row r="4" ht="39" customHeight="1">
       <c r="B4" s="35" t="n"/>
       <c r="C4" s="27" t="n"/>
       <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="58" t="n"/>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>Mr. X</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Mrs. Y</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>Other Person/ Family</t>
+        </is>
+      </c>
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J4" s="58" t="inlineStr">
+        <is>
+          <t>Optional Remarks /Comments</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15.5" customHeight="1">
       <c r="C5" s="28" t="n"/>
       <c r="D5" s="43" t="n"/>
-      <c r="E5" s="44" t="n"/>
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>Essential Spends</t>
+        </is>
+      </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30" t="n"/>
       <c r="H5" s="30" t="n"/>
@@ -17585,7 +18203,11 @@
     <row r="6" ht="15.5" customHeight="1">
       <c r="C6" s="28" t="n"/>
       <c r="D6" s="29" t="n"/>
-      <c r="E6" s="29" t="n"/>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>Rent, Maintenance &amp; Other Charges</t>
+        </is>
+      </c>
       <c r="F6" s="30" t="n"/>
       <c r="G6" s="30" t="n"/>
       <c r="H6" s="30" t="n"/>
@@ -17601,7 +18223,11 @@
         <f>D6+1</f>
         <v/>
       </c>
-      <c r="E7" s="29" t="n"/>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Living Expense (Groceries+Milk+Newspaper etc) </t>
+        </is>
+      </c>
       <c r="F7" s="30" t="n"/>
       <c r="G7" s="30" t="n"/>
       <c r="H7" s="30" t="n"/>
@@ -17617,7 +18243,11 @@
         <f>D7+1</f>
         <v/>
       </c>
-      <c r="E8" s="29" t="n"/>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Children Expense (Education Fees +Uniform+Extra Cirricular)</t>
+        </is>
+      </c>
       <c r="F8" s="30" t="n"/>
       <c r="G8" s="30" t="n"/>
       <c r="H8" s="30" t="n"/>
@@ -17633,7 +18263,11 @@
         <f>D8+1</f>
         <v/>
       </c>
-      <c r="E9" s="29" t="n"/>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Transport and Commute (Petrol+Car Main+Vehicle Insurance+ Cab+ Train etc)</t>
+        </is>
+      </c>
       <c r="F9" s="30" t="n"/>
       <c r="G9" s="30" t="n"/>
       <c r="H9" s="30" t="n"/>
@@ -17649,7 +18283,11 @@
         <f>D9+1</f>
         <v/>
       </c>
-      <c r="E10" s="29" t="n"/>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utilities (Gas , Electricity, Phone, Internet) </t>
+        </is>
+      </c>
       <c r="F10" s="30" t="n"/>
       <c r="G10" s="30" t="n"/>
       <c r="H10" s="30" t="n"/>
@@ -17665,7 +18303,11 @@
         <f>D10+1</f>
         <v/>
       </c>
-      <c r="E11" s="29" t="n"/>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>Other Expenses (Property Tax, Donation, Sports/Hobby, Contribution to Dependents etc.)</t>
+        </is>
+      </c>
       <c r="F11" s="30" t="n"/>
       <c r="G11" s="30" t="n"/>
       <c r="H11" s="30" t="n"/>
@@ -17681,7 +18323,11 @@
         <f>D11+1</f>
         <v/>
       </c>
-      <c r="E12" s="29" t="n"/>
+      <c r="E12" s="29" t="inlineStr">
+        <is>
+          <t>Lifestyle Expenses (Restaurant+Gym+Club+Gifts)</t>
+        </is>
+      </c>
       <c r="F12" s="30" t="n"/>
       <c r="G12" s="30" t="n"/>
       <c r="H12" s="30" t="n"/>
@@ -17697,7 +18343,11 @@
         <f>D12+1</f>
         <v/>
       </c>
-      <c r="E13" s="29" t="n"/>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mediacal Expenses </t>
+        </is>
+      </c>
       <c r="F13" s="30" t="n"/>
       <c r="G13" s="30" t="n"/>
       <c r="H13" s="30" t="n"/>
@@ -17713,7 +18363,11 @@
         <f>D13+1</f>
         <v/>
       </c>
-      <c r="E14" s="29" t="n"/>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>Insurance Premium - Health</t>
+        </is>
+      </c>
       <c r="F14" s="30" t="n"/>
       <c r="G14" s="30" t="n"/>
       <c r="H14" s="30" t="n"/>
@@ -17729,7 +18383,11 @@
         <f>D14+1</f>
         <v/>
       </c>
-      <c r="E15" s="29" t="n"/>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Insurance Premium - Life</t>
+        </is>
+      </c>
       <c r="F15" s="30" t="n"/>
       <c r="G15" s="30" t="n"/>
       <c r="H15" s="30" t="n"/>
@@ -17745,7 +18403,11 @@
         <f>D15+1</f>
         <v/>
       </c>
-      <c r="E16" s="29" t="n"/>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>Others (Please Specify)</t>
+        </is>
+      </c>
       <c r="F16" s="30" t="n"/>
       <c r="G16" s="30" t="n"/>
       <c r="H16" s="30" t="n"/>
@@ -17768,7 +18430,11 @@
     <row r="18" ht="15.5" customHeight="1">
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="43" t="n"/>
-      <c r="E18" s="44" t="n"/>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>Discretionary Spend</t>
+        </is>
+      </c>
       <c r="F18" s="30" t="n"/>
       <c r="G18" s="30" t="n"/>
       <c r="H18" s="30" t="n"/>
@@ -17778,7 +18444,11 @@
     <row r="19" ht="31" customHeight="1">
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="28" t="n"/>
-      <c r="E19" s="29" t="n"/>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>Entertainment and Lifestyle (Shoes, Apparels+Vacation+Entertainment)</t>
+        </is>
+      </c>
       <c r="F19" s="30" t="n"/>
       <c r="G19" s="30" t="n"/>
       <c r="H19" s="30" t="n"/>
@@ -17791,7 +18461,11 @@
     <row r="20" ht="15.5" customHeight="1">
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
-      <c r="E20" s="29" t="n"/>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>Others (Please Specify)</t>
+        </is>
+      </c>
       <c r="F20" s="30" t="n"/>
       <c r="G20" s="30" t="n"/>
       <c r="H20" s="30" t="n"/>
@@ -17814,7 +18488,11 @@
     <row r="22" ht="15.5" customHeight="1">
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="43" t="n"/>
-      <c r="E22" s="44" t="n"/>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>Loan Repayments</t>
+        </is>
+      </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n"/>
       <c r="H22" s="30" t="n"/>
@@ -17824,7 +18502,11 @@
     <row r="23" ht="15.5" customHeight="1">
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="29" t="n"/>
-      <c r="E23" s="29" t="n"/>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>EMI - Home Loan</t>
+        </is>
+      </c>
       <c r="F23" s="30" t="n"/>
       <c r="G23" s="30" t="n"/>
       <c r="H23" s="30" t="n"/>
@@ -17832,7 +18514,11 @@
         <f>SUM(F23:H23)</f>
         <v/>
       </c>
-      <c r="J23" s="31" t="n"/>
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>Payable until 2035</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.5" customHeight="1">
       <c r="C24" s="28" t="n"/>
@@ -17840,7 +18526,11 @@
         <f>D23+1</f>
         <v/>
       </c>
-      <c r="E24" s="29" t="n"/>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>EMI - Other Loan 1 (Pls Specify)</t>
+        </is>
+      </c>
       <c r="F24" s="30" t="n"/>
       <c r="G24" s="30" t="n"/>
       <c r="H24" s="30" t="n"/>
@@ -17856,7 +18546,11 @@
         <f>D24+1</f>
         <v/>
       </c>
-      <c r="E25" s="29" t="n"/>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>EMI - Other Loan2 (Pls Specify)</t>
+        </is>
+      </c>
       <c r="F25" s="30" t="n"/>
       <c r="G25" s="30" t="n"/>
       <c r="H25" s="30" t="n"/>
@@ -17869,7 +18563,11 @@
     <row r="26" ht="15.5" customHeight="1">
       <c r="C26" s="39" t="n"/>
       <c r="D26" s="39" t="n"/>
-      <c r="E26" s="40" t="n"/>
+      <c r="E26" s="40" t="inlineStr">
+        <is>
+          <t>Total Expenditure</t>
+        </is>
+      </c>
       <c r="F26" s="41">
         <f>SUM(F5:F21)</f>
         <v/>
@@ -18030,7 +18728,11 @@
       <c r="D2" s="73" t="n"/>
     </row>
     <row r="3" ht="14.5" customHeight="1">
-      <c r="B3" s="84" t="n"/>
+      <c r="B3" s="84" t="inlineStr">
+        <is>
+          <t>Total Emergency Corpus</t>
+        </is>
+      </c>
       <c r="C3" s="184" t="n"/>
       <c r="D3" s="153">
         <f>D5*6</f>
@@ -18038,12 +18740,20 @@
       </c>
     </row>
     <row r="4" ht="14.5" customHeight="1">
-      <c r="B4" s="84" t="n"/>
+      <c r="B4" s="84" t="inlineStr">
+        <is>
+          <t>Where is it parked?</t>
+        </is>
+      </c>
       <c r="C4" s="183" t="n"/>
       <c r="D4" s="73" t="n"/>
     </row>
     <row r="5" ht="14.5" customHeight="1">
-      <c r="B5" s="84" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Monthly household expense (for calculation)</t>
+        </is>
+      </c>
       <c r="C5" s="183">
         <f>'3_Expenses '!I26</f>
         <v/>
@@ -18054,7 +18764,11 @@
       </c>
     </row>
     <row r="6" ht="14.5" customHeight="1">
-      <c r="B6" s="84" t="n"/>
+      <c r="B6" s="84" t="inlineStr">
+        <is>
+          <t>Months of cover available</t>
+        </is>
+      </c>
       <c r="C6" s="185">
         <f>C3/C5</f>
         <v/>
@@ -18068,11 +18782,19 @@
       <c r="C8" s="4" t="n"/>
     </row>
     <row r="9" ht="14.5" customHeight="1">
-      <c r="B9" s="177" t="n"/>
+      <c r="B9" s="177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergency Fund </t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="178" t="n"/>
+      <c r="B10" s="178" t="inlineStr">
+        <is>
+          <t>1. BASE CALCULATION</t>
+        </is>
+      </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10">
         <f>'3_Expenses '!E6</f>
@@ -18096,7 +18818,11 @@
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="B12" s="180" t="n"/>
+      <c r="B12" s="180" t="inlineStr">
+        <is>
+          <t>Emergency Fund = Monthly Bare-Minimum Expenses × Coverage Months</t>
+        </is>
+      </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12">
         <f>'3_Expenses '!E8</f>
@@ -18120,7 +18846,11 @@
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="B14" s="195" t="n"/>
+      <c r="B14" s="195" t="inlineStr">
+        <is>
+          <t>Bare-minimum expenses include:</t>
+        </is>
+      </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14">
         <f>'3_Expenses '!E10</f>
@@ -18144,11 +18874,19 @@
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="B16" s="194" t="n"/>
+      <c r="B16" s="194" t="inlineStr">
+        <is>
+          <t>Household expenses (groceries, utilities, rent/maintenance)</t>
+        </is>
+      </c>
       <c r="C16" s="4" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="B17" s="194" t="n"/>
+      <c r="B17" s="194" t="inlineStr">
+        <is>
+          <t>EMIs (home loan, car loan, personal loan)</t>
+        </is>
+      </c>
       <c r="C17" s="4" t="n"/>
       <c r="D17">
         <f>'3_Expenses '!E13</f>
@@ -18160,7 +18898,11 @@
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="B18" s="194" t="n"/>
+      <c r="B18" s="194" t="inlineStr">
+        <is>
+          <t>Insurance premiums (term, health — non-negotiable)</t>
+        </is>
+      </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18">
         <f>'3_Expenses '!E14</f>
@@ -18172,7 +18914,11 @@
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
-      <c r="B19" s="194" t="n"/>
+      <c r="B19" s="194" t="inlineStr">
+        <is>
+          <t>Essential school fees if children are dependents</t>
+        </is>
+      </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19">
         <f>'3_Expenses '!E15</f>
@@ -18196,7 +18942,11 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="180" t="n"/>
+      <c r="B21" s="180" t="inlineStr">
+        <is>
+          <t>Exclude from base:</t>
+        </is>
+      </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21">
         <f>'3_Expenses '!E24</f>
@@ -18210,7 +18960,11 @@
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="181" t="n"/>
       <c r="C22" s="4" t="n"/>
-      <c r="D22" s="22" t="n"/>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="G22" s="362">
         <f>SUM(G10:G21)</f>
         <v/>
@@ -18218,15 +18972,27 @@
       <c r="H22" s="362" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="B23" s="194" t="n"/>
+      <c r="B23" s="194" t="inlineStr">
+        <is>
+          <t>SIPs / investment contributions</t>
+        </is>
+      </c>
       <c r="C23" s="4" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="B24" s="194" t="n"/>
+      <c r="B24" s="194" t="inlineStr">
+        <is>
+          <t>Discretionary spending (dining, travel, OTT)</t>
+        </is>
+      </c>
       <c r="C24" s="4" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="B25" s="194" t="n"/>
+      <c r="B25" s="194" t="inlineStr">
+        <is>
+          <t>Annual/irregular expenses</t>
+        </is>
+      </c>
       <c r="C25" s="4" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -18236,27 +19002,55 @@
       <c r="C27" s="4" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="B28" s="196" t="n"/>
+      <c r="B28" s="196" t="inlineStr">
+        <is>
+          <t>Emergency Fund Needed</t>
+        </is>
+      </c>
       <c r="C28" s="197" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="B29" s="198" t="n"/>
-      <c r="C29" s="199" t="n"/>
+      <c r="B29" s="198" t="inlineStr">
+        <is>
+          <t>Annual savings ratio is &lt; 30% of income</t>
+        </is>
+      </c>
+      <c r="C29" s="199" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="B30" s="198" t="n"/>
-      <c r="C30" s="199" t="n"/>
+      <c r="B30" s="198" t="inlineStr">
+        <is>
+          <t>Annual savings ratio is &lt; 30% of income</t>
+        </is>
+      </c>
+      <c r="C30" s="199" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="C31" s="4" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="B32" s="22" t="n"/>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Savings Ratio</t>
+        </is>
+      </c>
       <c r="C32" s="525">
         <f>'11. Inc Exp,Networth,Rec Invest'!I10</f>
         <v/>
       </c>
-      <c r="D32" s="22" t="n"/>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Include formula</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="C33" s="4" t="n"/>
@@ -21260,40 +22054,88 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="101" t="n"/>
+      <c r="B3" s="101" t="inlineStr">
+        <is>
+          <t>- CANARA ROBECO FOCUSED FUND - REGULAR GROWTH</t>
+        </is>
+      </c>
       <c r="D3" s="60" t="n"/>
       <c r="E3" s="59" t="n"/>
       <c r="H3" s="60" t="n"/>
       <c r="I3" s="59" t="n"/>
-      <c r="J3" s="102" t="n"/>
-      <c r="K3" s="103" t="n"/>
+      <c r="J3" s="102" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="K3" s="103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="101" t="n"/>
+      <c r="B4" s="101" t="inlineStr">
+        <is>
+          <t>- NIPPON INDIA FLEXI CAP FUND - GROWTH PLAN</t>
+        </is>
+      </c>
       <c r="D4" s="60" t="n"/>
       <c r="E4" s="59" t="n"/>
       <c r="H4" s="60" t="n"/>
       <c r="I4" s="59" t="n"/>
-      <c r="J4" s="102" t="n"/>
-      <c r="K4" s="103" t="n"/>
+      <c r="J4" s="102" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="K4" s="103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="101" t="n"/>
+      <c r="B5" s="101" t="inlineStr">
+        <is>
+          <t>- TATA SMALL CAP FUND - REGULAR PLAN - GROWTH</t>
+        </is>
+      </c>
       <c r="D5" s="60" t="n"/>
       <c r="E5" s="59" t="n"/>
       <c r="H5" s="60" t="n"/>
       <c r="I5" s="59" t="n"/>
-      <c r="J5" s="102" t="n"/>
-      <c r="K5" s="103" t="n"/>
+      <c r="J5" s="102" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="K5" s="103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="101" t="n"/>
+      <c r="B6" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- ICICI PRUDENTIAL MULTICAP FUND - GROWTH </t>
+        </is>
+      </c>
       <c r="D6" s="60" t="n"/>
       <c r="E6" s="59" t="n"/>
       <c r="H6" s="60" t="n"/>
       <c r="I6" s="59" t="n"/>
-      <c r="J6" s="102" t="n"/>
-      <c r="K6" s="103" t="n"/>
+      <c r="J6" s="102" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="K6" s="103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="59" t="n"/>
@@ -21434,7 +22276,11 @@
       <c r="K21" s="73" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="81" t="n"/>
+      <c r="B22" s="81" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="C22" s="82" t="n"/>
       <c r="D22" s="83" t="n"/>
       <c r="E22" s="81" t="n"/>
@@ -21452,7 +22298,11 @@
       <c r="K22" s="78" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="B25" s="65" t="n"/>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>Insert Rows between row2 and Row 25 for additional inputs</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -22519,190 +23369,358 @@
       <c r="I2" s="73" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="60" t="n"/>
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asian Paints </t>
+        </is>
+      </c>
       <c r="D3" s="59" t="n"/>
       <c r="E3" s="362" t="n"/>
-      <c r="F3" s="60" t="n"/>
+      <c r="F3" s="60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="G3" s="59" t="n"/>
       <c r="H3" s="60" t="n"/>
       <c r="I3" s="73" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="60" t="n"/>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis Bank </t>
+        </is>
+      </c>
       <c r="D4" s="59" t="n"/>
       <c r="E4" s="362" t="n"/>
-      <c r="F4" s="60" t="n"/>
+      <c r="F4" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G4" s="59" t="n"/>
       <c r="H4" s="60" t="n"/>
       <c r="I4" s="73" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="60" t="n"/>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bajaj Finance </t>
+        </is>
+      </c>
       <c r="D5" s="59" t="n"/>
       <c r="E5" s="362" t="n"/>
-      <c r="F5" s="60" t="n"/>
+      <c r="F5" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G5" s="59" t="n"/>
       <c r="H5" s="60" t="n"/>
       <c r="I5" s="73" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="60" t="n"/>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bharat Electronics </t>
+        </is>
+      </c>
       <c r="D6" s="59" t="n"/>
       <c r="E6" s="362" t="n"/>
-      <c r="F6" s="60" t="n"/>
+      <c r="F6" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G6" s="59" t="n"/>
       <c r="H6" s="60" t="n"/>
       <c r="I6" s="73" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="60" t="n"/>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bosch </t>
+        </is>
+      </c>
       <c r="D7" s="59" t="n"/>
       <c r="E7" s="362" t="n"/>
-      <c r="F7" s="60" t="n"/>
+      <c r="F7" s="60" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
       <c r="G7" s="59" t="n"/>
       <c r="H7" s="60" t="n"/>
       <c r="I7" s="73" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="60" t="n"/>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CreditAccess Grameen </t>
+        </is>
+      </c>
       <c r="D8" s="59" t="n"/>
       <c r="E8" s="362" t="n"/>
-      <c r="F8" s="60" t="n"/>
+      <c r="F8" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G8" s="59" t="n"/>
       <c r="H8" s="60" t="n"/>
       <c r="I8" s="73" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="60" t="n"/>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cupid </t>
+        </is>
+      </c>
       <c r="D9" s="59" t="n"/>
       <c r="E9" s="362" t="n"/>
-      <c r="F9" s="60" t="n"/>
+      <c r="F9" s="60" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
       <c r="G9" s="59" t="n"/>
       <c r="H9" s="60" t="n"/>
       <c r="I9" s="73" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="60" t="n"/>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eicher Motors </t>
+        </is>
+      </c>
       <c r="D10" s="59" t="n"/>
       <c r="E10" s="362" t="n"/>
-      <c r="F10" s="60" t="n"/>
+      <c r="F10" s="60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="G10" s="59" t="n"/>
       <c r="H10" s="60" t="n"/>
       <c r="I10" s="73" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="60" t="n"/>
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineers India </t>
+        </is>
+      </c>
       <c r="D11" s="59" t="n"/>
       <c r="E11" s="362" t="n"/>
-      <c r="F11" s="60" t="n"/>
+      <c r="F11" s="60" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
       <c r="G11" s="59" t="n"/>
       <c r="H11" s="60" t="n"/>
       <c r="I11" s="73" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="60" t="n"/>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Godfrey Phillips India </t>
+        </is>
+      </c>
       <c r="D12" s="59" t="n"/>
       <c r="E12" s="362" t="n"/>
-      <c r="F12" s="60" t="n"/>
+      <c r="F12" s="60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="G12" s="59" t="n"/>
       <c r="H12" s="60" t="n"/>
       <c r="I12" s="73" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="60" t="n"/>
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gujarat State Fertilizers &amp; Chemicls </t>
+        </is>
+      </c>
       <c r="D13" s="59" t="n"/>
       <c r="E13" s="362" t="n"/>
-      <c r="F13" s="60" t="n"/>
+      <c r="F13" s="60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="G13" s="59" t="n"/>
       <c r="H13" s="60" t="n"/>
       <c r="I13" s="73" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="60" t="n"/>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindustan Aeronautics </t>
+        </is>
+      </c>
       <c r="D14" s="59" t="n"/>
       <c r="E14" s="362" t="n"/>
-      <c r="F14" s="60" t="n"/>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G14" s="59" t="n"/>
       <c r="H14" s="60" t="n"/>
       <c r="I14" s="73" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="60" t="n"/>
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HCL Technologies </t>
+        </is>
+      </c>
       <c r="D15" s="59" t="n"/>
       <c r="E15" s="362" t="n"/>
-      <c r="F15" s="60" t="n"/>
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
       <c r="G15" s="59" t="n"/>
       <c r="H15" s="60" t="n"/>
       <c r="I15" s="73" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="60" t="n"/>
+      <c r="B16" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDFC Bank </t>
+        </is>
+      </c>
       <c r="D16" s="59" t="n"/>
       <c r="E16" s="362" t="n"/>
-      <c r="F16" s="60" t="n"/>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G16" s="59" t="n"/>
       <c r="H16" s="60" t="n"/>
       <c r="I16" s="73" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="60" t="n"/>
+      <c r="B17" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDFC Life Insurance Company </t>
+        </is>
+      </c>
       <c r="D17" s="59" t="n"/>
       <c r="E17" s="362" t="n"/>
-      <c r="F17" s="60" t="n"/>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G17" s="59" t="n"/>
       <c r="H17" s="60" t="n"/>
       <c r="I17" s="73" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="60" t="n"/>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICICI Prudential Asset Management Co </t>
+        </is>
+      </c>
       <c r="D18" s="59" t="n"/>
       <c r="E18" s="362" t="n"/>
-      <c r="F18" s="60" t="n"/>
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G18" s="59" t="n"/>
       <c r="H18" s="60" t="n"/>
       <c r="I18" s="73" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="60" t="n"/>
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICICI Bank </t>
+        </is>
+      </c>
       <c r="D19" s="59" t="n"/>
       <c r="E19" s="362" t="n"/>
-      <c r="F19" s="60" t="n"/>
+      <c r="F19" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G19" s="59" t="n"/>
       <c r="H19" s="60" t="n"/>
       <c r="I19" s="73" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="60" t="n"/>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICICI Lombard General Insurance Co </t>
+        </is>
+      </c>
       <c r="D20" s="59" t="n"/>
       <c r="E20" s="362" t="n"/>
-      <c r="F20" s="60" t="n"/>
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G20" s="59" t="n"/>
       <c r="H20" s="60" t="n"/>
       <c r="I20" s="73" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="60" t="n"/>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infosys </t>
+        </is>
+      </c>
       <c r="D21" s="59" t="n"/>
       <c r="E21" s="362" t="n"/>
-      <c r="F21" s="60" t="n"/>
+      <c r="F21" s="60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="G21" s="59" t="n"/>
       <c r="H21" s="60" t="n"/>
       <c r="I21" s="73" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="60" t="n"/>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITC </t>
+        </is>
+      </c>
       <c r="D22" s="59" t="n"/>
       <c r="E22" s="362" t="n"/>
-      <c r="F22" s="60" t="n"/>
+      <c r="F22" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G22" s="59" t="n"/>
       <c r="H22" s="60" t="n"/>
       <c r="I22" s="73" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="63" t="n"/>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITC Hotels </t>
+        </is>
+      </c>
       <c r="D23" s="61" t="n"/>
       <c r="E23" s="175" t="n"/>
-      <c r="F23" s="63" t="n"/>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="G23" s="61" t="n"/>
       <c r="H23" s="63" t="n"/>
       <c r="I23" s="74" t="n"/>
@@ -22724,21 +23742,33 @@
         <f>SUMIF(F$2:F$23,F26,E$2:E$23)</f>
         <v/>
       </c>
-      <c r="F26" s="60" t="n"/>
+      <c r="F26" s="60" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="E27" s="150">
         <f>SUMIF(F$2:F$23,F27,E$2:E$23)</f>
         <v/>
       </c>
-      <c r="F27" s="60" t="n"/>
+      <c r="F27" s="60" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="E28" s="150">
         <f>SUMIF(F$2:F$23,F28,E$2:E$23)</f>
         <v/>
       </c>
-      <c r="F28" s="60" t="n"/>
+      <c r="F28" s="60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="E29" s="150">
@@ -23749,8 +24779,16 @@
       <c r="G2" s="51" t="n"/>
     </row>
     <row r="3" ht="14.5" customHeight="1">
-      <c r="B3" s="66" t="n"/>
-      <c r="C3" s="66" t="n"/>
+      <c r="B3" s="66" t="inlineStr">
+        <is>
+          <t>Bonds</t>
+        </is>
+      </c>
+      <c r="C3" s="66" t="inlineStr">
+        <is>
+          <t>ICICI Corporate Bond 9%</t>
+        </is>
+      </c>
       <c r="D3" s="362" t="n"/>
       <c r="E3" s="362">
         <f>D3*109%</f>
@@ -23760,8 +24798,16 @@
       <c r="G3" s="51" t="n"/>
     </row>
     <row r="4" ht="14.5" customHeight="1">
-      <c r="B4" s="66" t="n"/>
-      <c r="C4" s="66" t="n"/>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C4" s="66" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
       <c r="D4" s="362" t="n"/>
       <c r="E4" s="362">
         <f>D4*1.5</f>
@@ -23771,35 +24817,67 @@
       <c r="G4" s="51" t="n"/>
     </row>
     <row r="5" ht="14.5" customHeight="1">
-      <c r="B5" s="66" t="n"/>
-      <c r="C5" s="66" t="n"/>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>PPF</t>
+        </is>
+      </c>
+      <c r="C5" s="66" t="inlineStr">
+        <is>
+          <t>PPF</t>
+        </is>
+      </c>
       <c r="D5" s="362" t="n"/>
       <c r="E5" s="362" t="n"/>
       <c r="F5" s="108" t="n"/>
       <c r="G5" s="51" t="n"/>
     </row>
     <row r="6" ht="14.5" customHeight="1">
-      <c r="B6" s="66" t="n"/>
-      <c r="C6" s="66" t="n"/>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>EPF</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>EPF</t>
+        </is>
+      </c>
       <c r="D6" s="362" t="n"/>
       <c r="E6" s="362" t="n"/>
       <c r="F6" s="108" t="n"/>
       <c r="G6" s="51" t="n"/>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="B7" s="66" t="n"/>
-      <c r="C7" s="66" t="n"/>
+      <c r="B7" s="66" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="C7" s="66" t="inlineStr">
+        <is>
+          <t>NPS by HDFC</t>
+        </is>
+      </c>
       <c r="D7" s="362" t="n"/>
       <c r="E7" s="362" t="n"/>
       <c r="F7" s="108" t="n"/>
       <c r="G7" s="51" t="n"/>
     </row>
     <row r="8" ht="14.5" customHeight="1">
-      <c r="B8" s="66" t="n"/>
+      <c r="B8" s="66" t="inlineStr">
+        <is>
+          <t>Post Office Saving A/c</t>
+        </is>
+      </c>
       <c r="C8" s="66" t="n"/>
       <c r="D8" s="362" t="n"/>
       <c r="E8" s="106" t="n"/>
-      <c r="F8" s="109" t="n"/>
+      <c r="F8" s="109" t="inlineStr">
+        <is>
+          <t>Immediate</t>
+        </is>
+      </c>
       <c r="G8" s="51" t="n"/>
     </row>
     <row r="9" ht="14.5" customHeight="1">
@@ -23811,7 +24889,11 @@
       <c r="G9" s="51" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="67" t="n"/>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="C10" s="67" t="n"/>
       <c r="D10" s="107">
         <f>SUM(D2:D9)</f>
@@ -27844,29 +28926,57 @@
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1">
-      <c r="B3" s="66" t="n"/>
+      <c r="B3" s="66" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
       <c r="C3" s="50" t="n"/>
-      <c r="D3" s="373" t="n"/>
+      <c r="D3" s="373" t="inlineStr">
+        <is>
+          <t>For Retirement</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="14.5" customHeight="1">
-      <c r="B4" s="66" t="n"/>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>PPF</t>
+        </is>
+      </c>
       <c r="C4" s="50" t="n"/>
       <c r="D4" s="66" t="n"/>
     </row>
     <row r="5" ht="14.5" customHeight="1">
-      <c r="B5" s="66" t="n"/>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
       <c r="C5" s="50" t="n"/>
       <c r="D5" s="66" t="n"/>
     </row>
     <row r="6" ht="14.5" customHeight="1">
-      <c r="B6" s="66" t="n"/>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>Direct Equity</t>
+        </is>
+      </c>
       <c r="C6" s="50" t="n"/>
       <c r="D6" s="66" t="n"/>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="B7" s="373" t="n"/>
+      <c r="B7" s="373" t="inlineStr">
+        <is>
+          <t>VPF</t>
+        </is>
+      </c>
       <c r="C7" s="50" t="n"/>
-      <c r="D7" s="373" t="n"/>
+      <c r="D7" s="373" t="inlineStr">
+        <is>
+          <t>For Retirement</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="14.5" customHeight="1">
       <c r="B8" s="66" t="n"/>
@@ -27879,7 +28989,11 @@
       <c r="D9" s="66" t="n"/>
     </row>
     <row r="10" ht="14.5" customHeight="1">
-      <c r="B10" s="80" t="n"/>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>Total Monthly Investments</t>
+        </is>
+      </c>
       <c r="C10" s="90">
         <f>SUM(C2:C7)</f>
         <v/>
@@ -27890,7 +29004,11 @@
       <c r="C11" s="4" t="n"/>
     </row>
     <row r="12" ht="14.5" customHeight="1">
-      <c r="B12" s="66" t="n"/>
+      <c r="B12" s="66" t="inlineStr">
+        <is>
+          <t>Insurance Premium</t>
+        </is>
+      </c>
       <c r="C12" s="50" t="n"/>
       <c r="D12" s="66" t="n"/>
     </row>
@@ -30928,7 +32046,11 @@
       <c r="F2" s="49" t="n"/>
     </row>
     <row r="3" ht="14" customHeight="1">
-      <c r="B3" s="122" t="n"/>
+      <c r="B3" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop </t>
+        </is>
+      </c>
       <c r="C3" s="50" t="n"/>
       <c r="D3" s="50" t="n"/>
       <c r="E3" s="50" t="n"/>
@@ -30977,7 +32099,11 @@
       <c r="F9" s="51" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="67" t="n"/>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="C10" s="77">
         <f>SUM(C2:C9)</f>
         <v/>
@@ -36255,9 +37381,17 @@
       <c r="D2" s="51" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="51" t="n"/>
+      <c r="B3" s="51" t="inlineStr">
+        <is>
+          <t>ESOP Of ABC Company</t>
+        </is>
+      </c>
       <c r="C3" s="72" t="n"/>
-      <c r="D3" s="32" t="n"/>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>ESOP current market price is Rs 100 Per share, 10000 ESOP vested . Shares not listed</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="51" t="n"/>
@@ -36290,7 +37424,11 @@
       <c r="D9" s="51" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="67" t="n"/>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="C10" s="79">
         <f>SUM(C2:C9)</f>
         <v/>
@@ -37331,22 +38469,38 @@
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1">
-      <c r="B3" s="84" t="n"/>
+      <c r="B3" s="84" t="inlineStr">
+        <is>
+          <t>Idle Cash for Investment</t>
+        </is>
+      </c>
       <c r="C3" s="85" t="n"/>
       <c r="D3" s="103" t="n"/>
     </row>
     <row r="4" ht="14.5" customHeight="1">
-      <c r="B4" s="84" t="n"/>
+      <c r="B4" s="84" t="inlineStr">
+        <is>
+          <t>FD Breakable for Investment</t>
+        </is>
+      </c>
       <c r="C4" s="85" t="n"/>
       <c r="D4" s="73" t="n"/>
     </row>
     <row r="5" ht="14.5" customHeight="1">
-      <c r="B5" s="84" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Bonus Expected for Investment</t>
+        </is>
+      </c>
       <c r="C5" s="85" t="n"/>
       <c r="D5" s="86" t="n"/>
     </row>
     <row r="6" ht="14.5" customHeight="1">
-      <c r="B6" s="84" t="n"/>
+      <c r="B6" s="84" t="inlineStr">
+        <is>
+          <t>Others (Pls Specify)</t>
+        </is>
+      </c>
       <c r="C6" s="87" t="n"/>
       <c r="D6" s="73" t="n"/>
     </row>
@@ -37366,7 +38520,11 @@
       <c r="D9" s="73" t="n"/>
     </row>
     <row r="10" ht="14.5" customHeight="1">
-      <c r="B10" s="89" t="n"/>
+      <c r="B10" s="89" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="C10" s="77">
         <f>SUM(C2:C9)</f>
         <v/>
@@ -40426,7 +41584,11 @@
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1">
-      <c r="B3" s="66" t="n"/>
+      <c r="B3" s="66" t="inlineStr">
+        <is>
+          <t>Car Loan</t>
+        </is>
+      </c>
       <c r="C3" s="49" t="n"/>
       <c r="D3" s="51" t="n"/>
       <c r="E3" s="52" t="n"/>
@@ -40434,7 +41596,11 @@
       <c r="G3" s="51" t="n"/>
     </row>
     <row r="4" ht="14.5" customHeight="1">
-      <c r="B4" s="66" t="n"/>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>Personal Loan</t>
+        </is>
+      </c>
       <c r="C4" s="49" t="n"/>
       <c r="D4" s="51" t="n"/>
       <c r="E4" s="52" t="n"/>
@@ -40442,7 +41608,11 @@
       <c r="G4" s="51" t="n"/>
     </row>
     <row r="5" ht="14.5" customHeight="1">
-      <c r="B5" s="66" t="n"/>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>Credit Card Dues</t>
+        </is>
+      </c>
       <c r="C5" s="49" t="n"/>
       <c r="D5" s="51" t="n"/>
       <c r="E5" s="52" t="n"/>
@@ -40450,7 +41620,11 @@
       <c r="G5" s="51" t="n"/>
     </row>
     <row r="6" ht="14.5" customHeight="1">
-      <c r="B6" s="66" t="n"/>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>Other Loans</t>
+        </is>
+      </c>
       <c r="C6" s="51" t="n"/>
       <c r="D6" s="51" t="n"/>
       <c r="E6" s="51" t="n"/>
@@ -40482,7 +41656,11 @@
       <c r="G9" s="51" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="67" t="n"/>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="C10" s="67">
         <f>SUM(C2:C9)</f>
         <v/>
@@ -43541,8 +44719,16 @@
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1">
-      <c r="B3" s="84" t="n"/>
-      <c r="C3" s="84" t="n"/>
+      <c r="B3" s="84" t="inlineStr">
+        <is>
+          <t>ULIP / Endowment</t>
+        </is>
+      </c>
+      <c r="C3" s="84" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
       <c r="D3" s="73" t="n"/>
       <c r="E3" s="73" t="n"/>
       <c r="F3" s="86" t="n"/>
@@ -43550,8 +44736,16 @@
       <c r="H3" s="73" t="n"/>
     </row>
     <row r="4" ht="14.5" customHeight="1">
-      <c r="B4" s="84" t="n"/>
-      <c r="C4" s="84" t="n"/>
+      <c r="B4" s="84" t="inlineStr">
+        <is>
+          <t>Health Insurance</t>
+        </is>
+      </c>
+      <c r="C4" s="84" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
       <c r="D4" s="103" t="n"/>
       <c r="E4" s="110" t="n"/>
       <c r="F4" s="86" t="n"/>
@@ -43559,13 +44753,29 @@
       <c r="H4" s="112" t="n"/>
     </row>
     <row r="5" ht="14.5" customHeight="1">
-      <c r="B5" s="371" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="103" t="n"/>
+      <c r="B5" s="371" t="inlineStr">
+        <is>
+          <t>Health Insurance - Family Floater</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="D5" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Star </t>
+        </is>
+      </c>
       <c r="E5" s="110" t="n"/>
       <c r="F5" s="86" t="n"/>
       <c r="G5" s="73" t="n"/>
-      <c r="H5" s="372" t="n"/>
+      <c r="H5" s="372" t="inlineStr">
+        <is>
+          <t>All 5 members covered</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="B6" s="73" t="n"/>
@@ -46637,232 +47847,468 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="11" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Responses and Scores</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="C6" s="21" t="n"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
       <c r="D6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="21" t="n"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
       <c r="D7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="C8" s="21" t="n"/>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
       <c r="D8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="C9" s="21" t="n"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Pan card Number</t>
+        </is>
+      </c>
       <c r="D9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" s="21" t="n"/>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Aadhar card</t>
+        </is>
+      </c>
       <c r="D10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" s="21" t="n"/>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Select computing for</t>
+        </is>
+      </c>
       <c r="D11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="C12" s="21" t="n"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Marital Status</t>
+        </is>
+      </c>
       <c r="D12" s="14" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="C13" s="21" t="n"/>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>No of Dependents and their details like wife, Son, Daughter, Father, Mother, Others (Pls Specify, No Dependents)</t>
+        </is>
+      </c>
       <c r="D13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="C14" s="21" t="n"/>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
       <c r="D14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="C15" s="21" t="n"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Occupation (Employed, Self-Employed / Business, Not engaged)</t>
+        </is>
+      </c>
       <c r="D15" s="14" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="C16" s="21" t="n"/>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Average Monthly Cash Inflow from different sources (Put different fields like salary, business, rentals, interest, others (Pls specify)</t>
+        </is>
+      </c>
       <c r="D16" s="14" t="n"/>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="C17" s="21" t="n"/>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Average Monthly Cash Outgo for different purposes like Rent, Other Household &amp; living (Grocery, Power, Conveyance etc) EMI (Pls specify purpose, ending date, EMI amount), Children Education, Insurance premium.</t>
+        </is>
+      </c>
       <c r="D17" s="14" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="C18" s="21" t="n"/>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Current Networth – Broken broadly in Real Estate, Jewellery, Stocks, MFs, Fixed Income instruments like FD / Bonds etc</t>
+        </is>
+      </c>
       <c r="D18" s="14" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="C19" s="21" t="n"/>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Current Liabilities: Loans Outstanding for Home, Vehicle, Personal, Credit Card etc</t>
+        </is>
+      </c>
       <c r="D19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="C20" s="21" t="n"/>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Liquidity (approx amount)</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="C21" s="21" t="n"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>What is your current income tax bracket?</t>
+        </is>
+      </c>
       <c r="D21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="C22" s="21" t="n"/>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>How old are you?</t>
+        </is>
+      </c>
       <c r="D22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="C23" s="21" t="n"/>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Number of Dependents</t>
+        </is>
+      </c>
       <c r="D23" s="14" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="C24" s="21" t="n"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Life Stage Assessment? How would you describe your financial situation.</t>
+        </is>
+      </c>
       <c r="D24" s="14" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="C25" s="21" t="n"/>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Income security? What is your primary source of income and describe your stablilty of income</t>
+        </is>
+      </c>
       <c r="D25" s="14" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="C26" s="21" t="n"/>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Investment Purpose What is the primary reason you are investing your funds?</t>
+        </is>
+      </c>
       <c r="D26" s="14" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="C27" s="21" t="n"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Investment Knowledge How familiar are you with investment matters and ﬁnancial markets?</t>
+        </is>
+      </c>
       <c r="D27" s="14" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="C28" s="21" t="n"/>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Investment time horizon? When do you expect to need a signiﬁcant portion of this money?</t>
+        </is>
+      </c>
       <c r="D28" s="14" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="C29" s="21" t="n"/>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Loss Tolerance How important is it for you to minimize ﬂuctuations or potential losses in your investment value?</t>
+        </is>
+      </c>
       <c r="D29" s="14" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="C30" s="21" t="n"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Loss Appetite What is the maximum aggregate loss you would be comfortable during one-year investment period?</t>
+        </is>
+      </c>
       <c r="D30" s="14" t="n"/>
     </row>
     <row r="31" ht="42" customHeight="1">
-      <c r="C31" s="21" t="n"/>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Reaction in case of Market Volatility How would you describe your reaction in case above loss benchmark is breached due to market fluctuations in your investment portfolio?</t>
+        </is>
+      </c>
       <c r="D31" s="14" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
-      <c r="C32" s="21" t="n"/>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Income Dependency How much do you rely on potential income from this investment portfolio to meet your living expenses or obligations?</t>
+        </is>
+      </c>
       <c r="D32" s="14" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="C33" s="21" t="n"/>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Investment Preferences Which types of investments are you most comfortable with or interested in?</t>
+        </is>
+      </c>
       <c r="D33" s="14" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="C34" s="21" t="n"/>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Emergency Fund Status Do you have an emergency fund covering 6-12 months of expenses outside this investment portfolio?</t>
+        </is>
+      </c>
       <c r="D34" s="14" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="C35" s="21" t="n"/>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Liquidity Requirements How often do you expect to withdraw money from this investment portfolio?</t>
+        </is>
+      </c>
       <c r="D35" s="14" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="C36" s="21" t="n"/>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Investment Constraints Do you have any speciﬁc investment restrictions or preferences?</t>
+        </is>
+      </c>
       <c r="D36" s="14" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="C37" s="21" t="n"/>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>Return Expectations What annual return do you realistically expect from your investments over the long term?</t>
+        </is>
+      </c>
       <c r="D37" s="14" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="C38" s="21" t="n"/>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Specific Financial Goals What is your primary financial goal for this investment? Purpose, Timeline and value at today’s date</t>
+        </is>
+      </c>
       <c r="D38" s="14" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="C39" s="21" t="n"/>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Exposure and investment in high risk assets What percentage of your total assets are you willing to invest in high-risk assets</t>
+        </is>
+      </c>
       <c r="D39" s="14" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="C40" s="21" t="n"/>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Risk or Return Priority How do you prioritize risk and return in your investment decisions?</t>
+        </is>
+      </c>
       <c r="D40" s="14" t="n"/>
     </row>
     <row r="41" hidden="1">
-      <c r="C41" s="21" t="n"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
       <c r="D41" s="14" t="n"/>
     </row>
     <row r="42" hidden="1">
-      <c r="C42" s="21" t="n"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Total score</t>
+        </is>
+      </c>
       <c r="D42" s="14" t="n"/>
     </row>
     <row r="43" hidden="1" ht="28" customHeight="1">
-      <c r="C43" s="21" t="n"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Life Stage Assessment? How would you describe your financial situation.</t>
+        </is>
+      </c>
       <c r="D43" s="14" t="n"/>
     </row>
     <row r="44" hidden="1" ht="28" customHeight="1">
-      <c r="C44" s="21" t="n"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Income security? What is your primary source of income and describe your stablilty of income</t>
+        </is>
+      </c>
       <c r="D44" s="14" t="n"/>
     </row>
     <row r="45" hidden="1" ht="28" customHeight="1">
-      <c r="C45" s="21" t="n"/>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Investment Purpose What is the primary reason you are investing your funds?</t>
+        </is>
+      </c>
       <c r="D45" s="14" t="n"/>
     </row>
     <row r="46" hidden="1" ht="28" customHeight="1">
-      <c r="C46" s="21" t="n"/>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Investment Knowledge How familiar are you with investment matters and ﬁnancial markets?</t>
+        </is>
+      </c>
       <c r="D46" s="14" t="n"/>
     </row>
     <row r="47" hidden="1" ht="28" customHeight="1">
-      <c r="C47" s="21" t="n"/>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>Investment time horizon? When do you expect to need a signiﬁcant portion of this money?</t>
+        </is>
+      </c>
       <c r="D47" s="14" t="n"/>
     </row>
     <row r="48" hidden="1" ht="28" customHeight="1">
-      <c r="C48" s="21" t="n"/>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Loss Tolerance How important is it for you to minimize ﬂuctuations or potential losses in your investment value?</t>
+        </is>
+      </c>
       <c r="D48" s="14" t="n"/>
     </row>
     <row r="49" hidden="1" ht="28" customHeight="1">
-      <c r="C49" s="21" t="n"/>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Loss Appetite What is the maximum aggregate loss you would be comfortable during one-year investment period?</t>
+        </is>
+      </c>
       <c r="D49" s="14" t="n"/>
     </row>
     <row r="50" hidden="1" ht="42" customHeight="1">
-      <c r="C50" s="21" t="n"/>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Reaction in case of Market Volatility How would you describe your reaction in case above loss benchmark is breached due to market fluctuations in your investment portfolio?</t>
+        </is>
+      </c>
       <c r="D50" s="14" t="n"/>
     </row>
     <row r="51" hidden="1" ht="42" customHeight="1">
-      <c r="C51" s="21" t="n"/>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Income Dependency How much do you rely on potential income from this investment portfolio to meet your living expenses or obligations?</t>
+        </is>
+      </c>
       <c r="D51" s="14" t="n"/>
     </row>
     <row r="52" hidden="1" ht="28" customHeight="1">
-      <c r="C52" s="21" t="n"/>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>Investment Preferences Which types of investments are you most comfortable with or interested in?</t>
+        </is>
+      </c>
       <c r="D52" s="14" t="n"/>
     </row>
     <row r="53" hidden="1" ht="28" customHeight="1">
-      <c r="C53" s="21" t="n"/>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>Emergency Fund Status Do you have an emergency fund covering 6-12 months of expenses outside this investment portfolio?</t>
+        </is>
+      </c>
       <c r="D53" s="14" t="n"/>
     </row>
     <row r="54" hidden="1" ht="28" customHeight="1">
-      <c r="C54" s="21" t="n"/>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>Liquidity Requirements How often do you expect to withdraw money from this investment portfolio?</t>
+        </is>
+      </c>
       <c r="D54" s="14" t="n"/>
     </row>
     <row r="55" hidden="1" ht="28" customHeight="1">
-      <c r="C55" s="21" t="n"/>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>Investment Constraints Do you have any speciﬁc investment restrictions or preferences?</t>
+        </is>
+      </c>
       <c r="D55" s="14" t="n"/>
     </row>
     <row r="56" hidden="1" ht="28" customHeight="1">
-      <c r="C56" s="21" t="n"/>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>Return Expectations What annual return do you realistically expect from your investments over the long term?</t>
+        </is>
+      </c>
       <c r="D56" s="14" t="n"/>
     </row>
     <row r="57" hidden="1" ht="28" customHeight="1">
-      <c r="C57" s="21" t="n"/>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>Specific Financial Goals What is your primary financial goal for this investment? Purpose, Timeline and value at today’s date</t>
+        </is>
+      </c>
       <c r="D57" s="14" t="n"/>
     </row>
     <row r="58" hidden="1" ht="28" customHeight="1">
-      <c r="C58" s="21" t="n"/>
+      <c r="C58" s="21" t="inlineStr">
+        <is>
+          <t>Exposure and investment in high risk assets What percentage of your total assets are you willing to invest in high-risk assets</t>
+        </is>
+      </c>
       <c r="D58" s="14" t="n"/>
     </row>
     <row r="59" hidden="1" ht="28" customHeight="1">
-      <c r="C59" s="21" t="n"/>
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>Risk or Return Priority How do you prioritize risk and return in your investment decisions?</t>
+        </is>
+      </c>
       <c r="D59" s="14" t="n"/>
     </row>
     <row r="60">
-      <c r="C60" s="21" t="n"/>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>Total Score</t>
+        </is>
+      </c>
       <c r="D60" s="17" t="n"/>
     </row>
     <row r="61">
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>Risk Profile</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>Moderately Aggressive</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
